--- a/templates/b2b_invoice_master.xlsx
+++ b/templates/b2b_invoice_master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet state="visible" name="MASTER" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="ITEM_MASTER" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="INPUT" sheetId="3" r:id="rId7"/>
+    <sheet sheetId="1" name="MASTER" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="ITEM_MASTER" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="INPUT" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -18,7 +18,7 @@
     <t>PMC CORPORATION</t>
   </si>
   <si>
-    <t>#309, 274 Samsung-ro, Yeongtong-gu, 
+    <t xml:space="preserve">#309, 274 Samsung-ro, Yeongtong-gu, 
 Suwon-si, Gyeonggi-do, Republic of Korea  16522</t>
   </si>
   <si>
@@ -42,18 +42,18 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Tahoma"/>
         <b/>
         <color theme="1"/>
-        <sz val="11.0"/>
+        <sz val="11"/>
+        <rFont val="Tahoma"/>
       </rPr>
       <t>VAT</t>
     </r>
     <r>
       <rPr>
+        <color theme="1"/>
+        <sz val="11"/>
         <rFont val="Tahoma"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t>: DE456630518</t>
     </r>
@@ -61,16 +61,16 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Tahoma"/>
         <b/>
         <color rgb="FF222222"/>
+        <rFont val="Tahoma"/>
       </rPr>
       <t>EORI</t>
     </r>
     <r>
       <rPr>
+        <color rgb="FF222222"/>
         <rFont val="Tahoma"/>
-        <color rgb="FF222222"/>
       </rPr>
       <t>: DE638885575817721</t>
     </r>
@@ -910,37 +910,38 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="166" formatCode="[$$]#,##0"/>
-    <numFmt numFmtId="167" formatCode="&quot;₩&quot;#,##0_);[Red]\(&quot;₩&quot;#,##0\)"/>
+    <numFmt numFmtId="167" formatCode="&quot;₩&quot;#,##0_);[Red](&quot;₩&quot;#,##0)"/>
     <numFmt numFmtId="168" formatCode="[$₩-412]#,##0"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
       <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="22.0"/>
       <color theme="1"/>
+      <sz val="22"/>
       <name val="Tahoma"/>
     </font>
     <font>
-      <sz val="11.0"/>
       <color theme="1"/>
+      <sz val="11"/>
       <name val="Tahoma"/>
     </font>
     <font>
       <b/>
       <u/>
-      <sz val="28.0"/>
       <color theme="1"/>
+      <sz val="28"/>
       <name val="Tahoma"/>
     </font>
     <font>
@@ -950,24 +951,24 @@
     <font>
       <b/>
       <u/>
-      <sz val="11.0"/>
       <color theme="1"/>
+      <sz val="11"/>
       <name val="Tahoma"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
       <color theme="1"/>
+      <sz val="11"/>
       <name val="Tahoma"/>
     </font>
     <font>
-      <sz val="11.0"/>
       <color rgb="FF0563C1"/>
+      <sz val="11"/>
       <name val="Malgun Gothic"/>
     </font>
     <font>
-      <sz val="11.0"/>
       <color rgb="FF333333"/>
+      <sz val="11"/>
       <name val="Tahoma"/>
     </font>
     <font>
@@ -975,74 +976,74 @@
       <name val="Tahoma"/>
     </font>
     <font>
-      <sz val="11.0"/>
       <color theme="1"/>
+      <sz val="11"/>
       <name val="Malgun Gothic"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
       <color theme="1"/>
+      <sz val="12"/>
       <name val="Malgun Gothic"/>
     </font>
     <font/>
     <font>
-      <sz val="11.0"/>
       <color rgb="FF000000"/>
+      <sz val="11"/>
       <name val="Tahoma"/>
     </font>
     <font>
       <b/>
       <u/>
-      <sz val="12.0"/>
       <color theme="1"/>
+      <sz val="12"/>
       <name val="Tahoma"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
       <color theme="1"/>
+      <sz val="11"/>
       <name val="Malgun Gothic"/>
     </font>
     <font>
-      <sz val="10.0"/>
       <color rgb="FF303030"/>
+      <sz val="10"/>
       <name val="Quattrocento Sans"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
       <color theme="1"/>
+      <sz val="11"/>
       <name val="Malgun Gothic"/>
     </font>
     <font>
-      <sz val="11.0"/>
       <color theme="1"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
       <color theme="1"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
       <strike/>
-      <sz val="11.0"/>
-      <color theme="1"/>
+      <sz val="11"/>
       <name val="Malgun Gothic"/>
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
       <color theme="1"/>
+      <sz val="13"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <i/>
-      <sz val="18.0"/>
       <color theme="1"/>
+      <sz val="18"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1051,7 +1052,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1084,8 +1085,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
-    <border/>
+  <borders count="39">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
@@ -1099,27 +1106,34 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -1129,6 +1143,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1143,6 +1158,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1157,6 +1173,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -1165,30 +1182,38 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -1198,22 +1223,29 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1222,9 +1254,11 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1233,64 +1267,72 @@
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -1305,6 +1347,7 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1319,6 +1362,7 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1333,27 +1377,38 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -1368,6 +1423,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1382,6 +1438,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1396,6 +1453,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -1410,6 +1468,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1424,6 +1483,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1438,6 +1498,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -1449,6 +1510,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -1463,6 +1526,7 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1477,6 +1541,7 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1491,27 +1556,34 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
@@ -1521,290 +1593,292 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="87">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="13" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="15" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="15" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="17" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="18" fillId="0" fontId="6" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="19" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="20" fillId="2" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="20" fillId="2" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="18" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="18" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="21" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="22" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="23" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="24" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="26" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="27" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="28" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="29" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="30" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="31" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="32" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf quotePrefix="1" borderId="30" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="31" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="32" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="30" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="31" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="32" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="30" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="33" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="34" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="35" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="36" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="37" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="38" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="39" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="37" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="38" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="39" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-  <xdr:oneCellAnchor>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
@@ -1814,25 +1888,36 @@
     <xdr:ext cx="2019300" cy="904875"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg" title="이미지"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
+    <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>952500</xdr:colOff>
@@ -1842,37 +1927,36 @@
     <xdr:ext cx="1076325" cy="476250"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="이미지"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
+    <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2070,28 +2154,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:AA1020"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.43"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="2.71"/>
-    <col customWidth="1" min="2" max="2" width="5.43"/>
-    <col customWidth="1" min="3" max="3" width="14.57"/>
-    <col customWidth="1" min="4" max="4" width="1.29"/>
-    <col customWidth="1" min="5" max="5" width="14.86"/>
-    <col customWidth="1" min="6" max="6" width="47.86"/>
-    <col customWidth="1" min="7" max="7" width="8.71"/>
-    <col customWidth="1" min="8" max="8" width="2.57"/>
-    <col customWidth="1" min="9" max="9" width="12.43"/>
-    <col customWidth="1" min="11" max="11" width="11.86"/>
-    <col customWidth="1" min="12" max="12" width="27.43"/>
-    <col customWidth="1" min="13" max="13" width="12.29"/>
-    <col customWidth="1" min="14" max="27" width="8.71"/>
+    <col min="1" max="1" width="2.71" customWidth="1"/>
+    <col min="2" max="2" width="5.43" customWidth="1"/>
+    <col min="3" max="3" width="14.57" customWidth="1"/>
+    <col min="4" max="4" width="1.29" customWidth="1"/>
+    <col min="5" max="5" width="14.86" customWidth="1"/>
+    <col min="6" max="6" width="47.86" customWidth="1"/>
+    <col min="7" max="7" width="8.71" customWidth="1"/>
+    <col min="8" max="8" width="2.57" customWidth="1"/>
+    <col min="9" max="9" width="12.43" customWidth="1"/>
+    <col min="11" max="11" width="11.86" customWidth="1"/>
+    <col min="12" max="12" width="27.43" customWidth="1"/>
+    <col min="13" max="13" width="12.29" customWidth="1"/>
+    <col min="14" max="27" width="8.71" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.0" customHeight="1">
+    <row r="1" ht="21" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2104,36 +2189,82 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" ht="59.25" customHeight="1">
+    <row r="2" ht="59.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" ht="37.5" customHeight="1">
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+    </row>
+    <row r="3" ht="37.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" ht="16.5" customHeight="1">
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" ht="26.25" customHeight="1">
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4"/>
+    </row>
+    <row r="5" ht="26.25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5"/>
       <c r="T5" s="5"/>
     </row>
-    <row r="6" ht="17.25" customHeight="1">
+    <row r="6" ht="17.25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
       <c r="T6" s="5"/>
     </row>
-    <row r="7" ht="16.5" customHeight="1">
+    <row r="7" ht="16.5" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
         <v>4</v>
@@ -2147,10 +2278,11 @@
       <c r="I7" s="9" t="s">
         <v>5</v>
       </c>
+      <c r="J7"/>
       <c r="K7" s="7"/>
       <c r="T7" s="5"/>
     </row>
-    <row r="8" ht="16.5" customHeight="1">
+    <row r="8" ht="16.5" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="7" t="s">
         <v>6</v>
@@ -2166,7 +2298,7 @@
       <c r="K8" s="7"/>
       <c r="T8" s="5"/>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
+    <row r="9" ht="16.5" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="B9" s="10" t="s">
         <v>7</v>
@@ -2182,11 +2314,12 @@
       <c r="K9" s="7"/>
       <c r="T9" s="5"/>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
+    <row r="10" ht="16.5" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="11" t="s">
         <v>8</v>
       </c>
+      <c r="C10"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
@@ -2198,7 +2331,7 @@
       <c r="O10" s="13"/>
       <c r="T10" s="5"/>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
+    <row r="11" ht="16.5" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="14" t="s">
         <v>9</v>
@@ -2215,7 +2348,7 @@
       <c r="O11" s="13"/>
       <c r="T11" s="5"/>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
+    <row r="12" ht="16.5" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -2230,11 +2363,19 @@
       <c r="O12" s="13"/>
       <c r="T12" s="5"/>
     </row>
-    <row r="13" ht="34.5" customHeight="1">
+    <row r="13" ht="34.5" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="15"/>
       <c r="B13" s="15" t="s">
         <v>10</v>
       </c>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
       <c r="K13" s="15"/>
       <c r="L13" s="16"/>
       <c r="M13" s="17"/>
@@ -2253,11 +2394,11 @@
       <c r="Z13" s="16"/>
       <c r="AA13" s="16"/>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
+    <row r="14" ht="16.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="18"/>
       <c r="B14" s="18"/>
     </row>
-    <row r="15" ht="16.5" customHeight="1">
+    <row r="15" ht="16.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="19"/>
       <c r="B15" s="19"/>
       <c r="C15" s="11" t="s">
@@ -2272,7 +2413,7 @@
       <c r="L15" s="20"/>
       <c r="M15" s="21"/>
     </row>
-    <row r="16" ht="16.5" customHeight="1">
+    <row r="16" ht="16.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="19"/>
       <c r="B16" s="19"/>
       <c r="C16" s="11" t="s">
@@ -2285,7 +2426,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1">
+    <row r="17" ht="16.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="19"/>
       <c r="B17" s="19"/>
       <c r="C17" s="11" t="s">
@@ -2298,7 +2439,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1">
+    <row r="18" ht="16.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="19"/>
       <c r="B18" s="19"/>
       <c r="C18" s="11" t="s">
@@ -2311,7 +2452,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1">
+    <row r="19" ht="16.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="19"/>
       <c r="B19" s="19"/>
       <c r="C19" s="11" t="s">
@@ -2324,7 +2465,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1">
+    <row r="20" ht="16.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="19"/>
       <c r="B20" s="19"/>
       <c r="C20" s="11" t="s">
@@ -2336,14 +2477,23 @@
       <c r="E20" s="7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="21" ht="16.5" customHeight="1">
+      <c r="N20"/>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+    </row>
+    <row r="21" ht="16.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="19"/>
       <c r="B21" s="19"/>
       <c r="C21" s="11"/>
       <c r="E21" s="7"/>
-    </row>
-    <row r="22" ht="16.5" customHeight="1">
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+    </row>
+    <row r="22" ht="16.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="22" t="s">
         <v>24</v>
@@ -2364,11 +2514,16 @@
       <c r="J22" s="27" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="23" ht="20.25" customHeight="1">
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
+      <c r="Q22"/>
+    </row>
+    <row r="23" ht="20.25" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="28">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C23" s="29"/>
       <c r="D23" s="30"/>
@@ -2378,11 +2533,16 @@
       <c r="H23" s="33"/>
       <c r="I23" s="34"/>
       <c r="J23" s="35"/>
-    </row>
-    <row r="24" ht="20.25" customHeight="1">
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+    </row>
+    <row r="24" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="28">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C24" s="36"/>
       <c r="D24" s="37"/>
@@ -2393,10 +2553,10 @@
       <c r="I24" s="34"/>
       <c r="J24" s="35"/>
     </row>
-    <row r="25" ht="20.25" customHeight="1">
+    <row r="25" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="28">
-        <v>4.0</v>
+        <v>3</v>
       </c>
       <c r="C25" s="36"/>
       <c r="D25" s="37"/>
@@ -2407,10 +2567,10 @@
       <c r="I25" s="34"/>
       <c r="J25" s="35"/>
     </row>
-    <row r="26" ht="20.25" customHeight="1">
+    <row r="26" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="28">
-        <v>5.0</v>
+        <v>4</v>
       </c>
       <c r="C26" s="36"/>
       <c r="D26" s="37"/>
@@ -2421,10 +2581,10 @@
       <c r="I26" s="34"/>
       <c r="J26" s="35"/>
     </row>
-    <row r="27" ht="20.25" customHeight="1">
+    <row r="27" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="28">
-        <v>6.0</v>
+        <v>5</v>
       </c>
       <c r="C27" s="36"/>
       <c r="D27" s="37"/>
@@ -2435,10 +2595,10 @@
       <c r="I27" s="34"/>
       <c r="J27" s="35"/>
     </row>
-    <row r="28" ht="20.25" customHeight="1">
+    <row r="28" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="28">
-        <v>7.0</v>
+        <v>6</v>
       </c>
       <c r="C28" s="36"/>
       <c r="D28" s="37"/>
@@ -2449,1762 +2609,1974 @@
       <c r="I28" s="34"/>
       <c r="J28" s="35"/>
     </row>
-    <row r="29" ht="20.25" customHeight="1">
+    <row r="29" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="28">
-        <v>8.0</v>
-      </c>
-      <c r="C29" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="36"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="35"/>
+    </row>
+    <row r="30" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+      <c r="B30" s="28">
+        <v>8</v>
+      </c>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="35"/>
+    </row>
+    <row r="31" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="3"/>
+      <c r="B31" s="28">
+        <v>9</v>
+      </c>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="35"/>
+    </row>
+    <row r="32" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="3"/>
+      <c r="B32" s="28">
+        <v>10</v>
+      </c>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="35"/>
+    </row>
+    <row r="33" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="3"/>
+      <c r="B33" s="28">
+        <v>11</v>
+      </c>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="35"/>
+    </row>
+    <row r="34" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+      <c r="B34" s="28">
+        <v>12</v>
+      </c>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="35"/>
+    </row>
+    <row r="35" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+      <c r="B35" s="28">
+        <v>13</v>
+      </c>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="35"/>
+    </row>
+    <row r="36" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="3"/>
+      <c r="B36" s="28">
+        <v>14</v>
+      </c>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="34"/>
+      <c r="J36" s="35"/>
+    </row>
+    <row r="37" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="3"/>
+      <c r="B37" s="28">
+        <v>15</v>
+      </c>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="34"/>
+      <c r="J37" s="35"/>
+    </row>
+    <row r="38" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="3"/>
+      <c r="B38" s="28">
+        <v>16</v>
+      </c>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="34"/>
+      <c r="J38" s="35"/>
+    </row>
+    <row r="39" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="3"/>
+      <c r="B39" s="28">
+        <v>17</v>
+      </c>
+      <c r="C39" s="36"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="34"/>
+      <c r="J39" s="35"/>
+    </row>
+    <row r="40" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="3"/>
+      <c r="B40" s="28">
+        <v>18</v>
+      </c>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="34"/>
+      <c r="J40" s="35"/>
+    </row>
+    <row r="41" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="3"/>
+      <c r="B41" s="28">
+        <v>19</v>
+      </c>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="34"/>
+      <c r="J41" s="35"/>
+    </row>
+    <row r="42" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="3"/>
+      <c r="B42" s="28">
+        <v>20</v>
+      </c>
+      <c r="C42" s="36"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="35"/>
+    </row>
+    <row r="43" ht="20.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="3"/>
+      <c r="B43" s="28">
+        <v>21</v>
+      </c>
+      <c r="C43" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="32">
-        <f>G30/30</f>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="32">
+        <f>G44/30</f>
         <v>0</v>
       </c>
-      <c r="H29" s="33"/>
-      <c r="I29" s="34">
-        <v>100.0</v>
-      </c>
-      <c r="J29" s="35">
-        <f>G29*I29</f>
+      <c r="H43" s="32"/>
+      <c r="I43" s="34">
+        <v>100</v>
+      </c>
+      <c r="J43" s="35">
+        <f>G43*I43</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1">
-      <c r="A30" s="8"/>
-      <c r="B30" s="38" t="s">
+    <row r="44" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="8"/>
+      <c r="B44" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="39">
-        <f>SUM(G23:H28)</f>
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="39">
+        <f>SUM(G23:H42)</f>
         <v>0</v>
       </c>
-      <c r="H30" s="39" t="s">
+      <c r="H44" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="I30" s="40"/>
-      <c r="J30" s="41">
-        <f>sum(J23:J29)</f>
+      <c r="I44" s="40"/>
+      <c r="J44" s="41">
+        <f>SUM(J23:J43)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="28.5" customHeight="1">
-      <c r="A31" s="42"/>
-      <c r="B31" s="42" t="s">
+    <row r="45" ht="28.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="42"/>
+      <c r="B45" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-    </row>
-    <row r="32" ht="16.5" customHeight="1">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="F32" s="7"/>
-    </row>
-    <row r="33" ht="16.5" customHeight="1">
-      <c r="A33" s="43"/>
-      <c r="B33" s="43" t="s">
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+    </row>
+    <row r="46" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="F46" s="7"/>
+    </row>
+    <row r="47" ht="16.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="43"/>
+      <c r="B47" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="F33" s="7"/>
-    </row>
-    <row r="34" ht="7.5" customHeight="1">
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="7"/>
-    </row>
-    <row r="35" ht="16.5" customHeight="1">
-      <c r="A35" s="8"/>
-      <c r="B35" s="44" t="s">
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="F47" s="7"/>
+    </row>
+    <row r="48" ht="7.5" customHeight="1" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M48" s="8"/>
+      <c r="N48" s="8"/>
+      <c r="O48" s="7"/>
+    </row>
+    <row r="49" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="45"/>
-      <c r="D35" s="5" t="s">
+      <c r="C49" s="44"/>
+      <c r="D49" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E49" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G35" s="45"/>
-      <c r="L35" s="46"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="7"/>
-    </row>
-    <row r="36" ht="16.5" customHeight="1">
-      <c r="A36" s="8"/>
-      <c r="B36" s="44" t="s">
+      <c r="G49" s="44"/>
+      <c r="L49" s="45"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="8"/>
+      <c r="O49" s="7"/>
+    </row>
+    <row r="50" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="8"/>
+      <c r="B50" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D50" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E50" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="7"/>
-    </row>
-    <row r="37" ht="16.5" customHeight="1">
-      <c r="E37" s="7" t="s">
+      <c r="M50" s="8"/>
+      <c r="N50" s="8"/>
+      <c r="O50" s="7"/>
+    </row>
+    <row r="51" ht="16.5" customHeight="1" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E51" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="7"/>
-    </row>
-    <row r="38" ht="16.5" customHeight="1">
-      <c r="M38" s="8"/>
-      <c r="N38" s="45"/>
-      <c r="P38" s="7"/>
-      <c r="Q38" s="7"/>
-    </row>
-    <row r="39" ht="16.5" customHeight="1">
-      <c r="A39" s="45"/>
-      <c r="B39" s="45"/>
-      <c r="C39" s="45"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="7"/>
-    </row>
-    <row r="40" ht="16.5" customHeight="1">
-      <c r="P40" s="7"/>
-    </row>
-    <row r="41" ht="16.5" customHeight="1">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="G41" s="45"/>
-    </row>
-    <row r="42" ht="16.5" customHeight="1">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="G42" s="45"/>
-      <c r="Q42" s="5"/>
-      <c r="S42" s="5"/>
-    </row>
-    <row r="43" ht="16.5" customHeight="1">
-      <c r="Q43" s="5"/>
-      <c r="S43" s="5"/>
-    </row>
-    <row r="44" ht="16.5" customHeight="1">
-      <c r="F44" s="47" t="s">
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+      <c r="O51" s="7"/>
+    </row>
+    <row r="52" ht="16.5" customHeight="1" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="M52" s="8"/>
+      <c r="N52" s="44"/>
+      <c r="P52" s="7"/>
+      <c r="Q52" s="7"/>
+    </row>
+    <row r="53" ht="16.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A53" s="44"/>
+      <c r="B53" s="44"/>
+      <c r="C53" s="44"/>
+      <c r="P53" s="7"/>
+      <c r="Q53" s="7"/>
+    </row>
+    <row r="54" ht="16.5" customHeight="1" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P54" s="7"/>
+    </row>
+    <row r="55" ht="16.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="G55" s="44"/>
+    </row>
+    <row r="56" ht="16.5" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A56" s="7"/>
+      <c r="B56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="G56" s="44"/>
+      <c r="Q56" s="5"/>
+      <c r="S56" s="5"/>
+    </row>
+    <row r="57" ht="16.5" customHeight="1" spans="17:19" x14ac:dyDescent="0.25">
+      <c r="Q57" s="5"/>
+      <c r="S57" s="5"/>
+    </row>
+    <row r="58" ht="16.5" customHeight="1" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="F58" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
-      <c r="Q44" s="5"/>
-      <c r="S44" s="5"/>
-    </row>
-    <row r="45" ht="16.5" customHeight="1">
-      <c r="I45" s="20"/>
-      <c r="J45" s="48"/>
-      <c r="K45" s="48"/>
-      <c r="S45" s="5"/>
-    </row>
-    <row r="46" ht="16.5" customHeight="1">
-      <c r="S46" s="5"/>
-    </row>
-    <row r="47" ht="16.5" customHeight="1">
-      <c r="C47" s="49"/>
-      <c r="D47" s="49"/>
-      <c r="E47" s="49"/>
-      <c r="F47" s="49"/>
-      <c r="G47" s="49"/>
-      <c r="H47" s="49"/>
-      <c r="I47" s="49"/>
-      <c r="J47" s="49"/>
-      <c r="K47" s="49"/>
-      <c r="S47" s="5"/>
-    </row>
-    <row r="48" ht="16.5" customHeight="1">
-      <c r="A48" s="50"/>
-      <c r="B48" s="50"/>
-      <c r="C48" s="49"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="49"/>
-      <c r="G48" s="49"/>
-      <c r="H48" s="49"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="49"/>
-      <c r="K48" s="49"/>
-      <c r="S48" s="5"/>
-    </row>
-    <row r="49" ht="16.5" customHeight="1">
-      <c r="A49" s="50"/>
-      <c r="B49" s="50"/>
-      <c r="C49" s="51"/>
-      <c r="D49" s="52"/>
-      <c r="E49" s="53"/>
-      <c r="F49" s="53"/>
-      <c r="G49" s="53"/>
-      <c r="H49" s="51"/>
-      <c r="I49" s="51"/>
-      <c r="J49" s="51"/>
-      <c r="K49" s="54"/>
-      <c r="S49" s="5"/>
-    </row>
-    <row r="50" ht="16.5" customHeight="1">
-      <c r="A50" s="55"/>
-      <c r="B50" s="55"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="K50" s="56"/>
-      <c r="S50" s="5"/>
-    </row>
-    <row r="51" ht="16.5" customHeight="1">
-      <c r="A51" s="57"/>
-      <c r="B51" s="57"/>
-      <c r="C51" s="51"/>
-      <c r="D51" s="51"/>
-      <c r="K51" s="56"/>
-      <c r="S51" s="5"/>
-    </row>
-    <row r="52" ht="16.5" customHeight="1">
-      <c r="C52" s="51"/>
-      <c r="D52" s="51"/>
-      <c r="E52" s="51"/>
-      <c r="F52" s="51"/>
-      <c r="G52" s="51"/>
-      <c r="H52" s="51"/>
-      <c r="I52" s="51"/>
-      <c r="J52" s="51"/>
-      <c r="K52" s="56"/>
-      <c r="S52" s="5"/>
-    </row>
-    <row r="53" ht="16.5" customHeight="1">
-      <c r="C53" s="51"/>
-      <c r="D53" s="51"/>
-      <c r="E53" s="51"/>
-      <c r="F53" s="51"/>
-      <c r="G53" s="51"/>
-      <c r="H53" s="51"/>
-      <c r="I53" s="51"/>
-      <c r="J53" s="51"/>
-      <c r="K53" s="56"/>
-      <c r="S53" s="5"/>
-    </row>
-    <row r="54" ht="16.5" customHeight="1">
-      <c r="C54" s="51"/>
-      <c r="D54" s="51"/>
-      <c r="E54" s="51"/>
-      <c r="F54" s="51"/>
-      <c r="G54" s="51"/>
-      <c r="H54" s="51"/>
-      <c r="I54" s="51"/>
-      <c r="J54" s="51"/>
-      <c r="K54" s="56"/>
-      <c r="S54" s="5"/>
-    </row>
-    <row r="55" ht="16.5" customHeight="1">
-      <c r="C55" s="51"/>
-      <c r="D55" s="51"/>
-      <c r="E55" s="51"/>
-      <c r="F55" s="51"/>
-      <c r="G55" s="51"/>
-      <c r="H55" s="51"/>
-      <c r="I55" s="51"/>
-      <c r="J55" s="51"/>
-      <c r="K55" s="56"/>
-      <c r="S55" s="5"/>
-    </row>
-    <row r="56" ht="16.5" customHeight="1">
-      <c r="C56" s="51"/>
-      <c r="D56" s="51"/>
-      <c r="E56" s="51"/>
-      <c r="F56" s="51"/>
-      <c r="G56" s="51"/>
-      <c r="H56" s="51"/>
-      <c r="I56" s="51"/>
-      <c r="J56" s="51"/>
-      <c r="K56" s="56"/>
-    </row>
-    <row r="57" ht="16.5" customHeight="1">
-      <c r="C57" s="51"/>
-      <c r="D57" s="51"/>
-      <c r="H57" s="51"/>
-      <c r="I57" s="51"/>
-      <c r="J57" s="51"/>
-      <c r="K57" s="56"/>
-    </row>
-    <row r="58" ht="16.5" customHeight="1">
-      <c r="C58" s="51"/>
-      <c r="D58" s="51"/>
-      <c r="E58" s="51"/>
-      <c r="F58" s="51"/>
-      <c r="G58" s="51"/>
-      <c r="H58" s="51"/>
-      <c r="I58" s="51"/>
-      <c r="J58" s="51"/>
-      <c r="K58" s="56"/>
-    </row>
-    <row r="59" ht="16.5" customHeight="1">
-      <c r="C59" s="51"/>
-      <c r="D59" s="51"/>
-      <c r="E59" s="51"/>
-      <c r="F59" s="51"/>
-      <c r="G59" s="51"/>
-      <c r="H59" s="51"/>
-      <c r="I59" s="51"/>
-      <c r="J59" s="51"/>
-      <c r="K59" s="56"/>
-    </row>
-    <row r="60" ht="16.5" customHeight="1">
-      <c r="C60" s="51"/>
-      <c r="D60" s="51"/>
-      <c r="E60" s="51"/>
-      <c r="F60" s="51"/>
-      <c r="G60" s="51"/>
-      <c r="H60" s="51"/>
-      <c r="I60" s="51"/>
-      <c r="J60" s="51"/>
-      <c r="K60" s="56"/>
-    </row>
-    <row r="61" ht="16.5" customHeight="1">
-      <c r="C61" s="51"/>
-      <c r="D61" s="51"/>
-      <c r="E61" s="51"/>
-      <c r="F61" s="51"/>
-      <c r="G61" s="51"/>
-      <c r="H61" s="51"/>
-      <c r="I61" s="51"/>
-      <c r="J61" s="51"/>
-      <c r="K61" s="56"/>
-    </row>
-    <row r="62" ht="16.5" customHeight="1">
-      <c r="C62" s="51"/>
-      <c r="D62" s="51"/>
-      <c r="E62" s="51"/>
-      <c r="F62" s="51"/>
-      <c r="G62" s="51"/>
-      <c r="H62" s="51"/>
-      <c r="I62" s="51"/>
-      <c r="J62" s="51"/>
-      <c r="K62" s="56"/>
-    </row>
-    <row r="63" ht="16.5" customHeight="1">
-      <c r="C63" s="51"/>
+      <c r="G58" s="46"/>
+      <c r="H58" s="36"/>
+      <c r="I58" s="36"/>
+      <c r="J58" s="36"/>
+      <c r="Q58" s="5"/>
+      <c r="S58" s="5"/>
+    </row>
+    <row r="59" ht="16.5" customHeight="1" spans="9:19" x14ac:dyDescent="0.25">
+      <c r="I59" s="20"/>
+      <c r="J59" s="47"/>
+      <c r="K59" s="47"/>
+      <c r="S59" s="5"/>
+    </row>
+    <row r="60" ht="16.5" customHeight="1" spans="19:19" x14ac:dyDescent="0.25">
+      <c r="S60" s="5"/>
+    </row>
+    <row r="61" ht="16.5" customHeight="1" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C61" s="48"/>
+      <c r="D61" s="48"/>
+      <c r="E61" s="48"/>
+      <c r="F61" s="48"/>
+      <c r="G61" s="48"/>
+      <c r="H61" s="48"/>
+      <c r="I61" s="48"/>
+      <c r="J61" s="48"/>
+      <c r="K61" s="48"/>
+      <c r="S61" s="5"/>
+    </row>
+    <row r="62" ht="16.5" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A62" s="49"/>
+      <c r="B62" s="49"/>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="J62" s="48"/>
+      <c r="K62" s="48"/>
+      <c r="S62" s="5"/>
+    </row>
+    <row r="63" ht="16.5" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A63" s="49"/>
+      <c r="B63" s="49"/>
+      <c r="C63" s="50"/>
       <c r="D63" s="51"/>
-      <c r="E63" s="51"/>
-      <c r="F63" s="51"/>
-      <c r="G63" s="51"/>
-      <c r="H63" s="51"/>
-      <c r="I63" s="51"/>
-      <c r="J63" s="51"/>
-      <c r="K63" s="56"/>
-    </row>
-    <row r="64" ht="16.5" customHeight="1">
-      <c r="C64" s="51"/>
-      <c r="D64" s="51"/>
-      <c r="E64" s="51"/>
-      <c r="F64" s="51"/>
-      <c r="G64" s="51"/>
-      <c r="H64" s="51"/>
-      <c r="I64" s="51"/>
-      <c r="J64" s="51"/>
-      <c r="K64" s="56"/>
-    </row>
-    <row r="65" ht="16.5" customHeight="1">
-      <c r="C65" s="51"/>
-      <c r="D65" s="51"/>
-      <c r="E65" s="51"/>
-      <c r="F65" s="51"/>
-      <c r="G65" s="51"/>
-      <c r="H65" s="51"/>
-      <c r="I65" s="51"/>
-      <c r="J65" s="51"/>
-      <c r="K65" s="56"/>
-    </row>
-    <row r="66" ht="16.5" customHeight="1">
-      <c r="C66" s="51"/>
-      <c r="D66" s="51"/>
-      <c r="E66" s="51"/>
-      <c r="F66" s="51"/>
-      <c r="G66" s="51"/>
-      <c r="H66" s="51"/>
-      <c r="I66" s="51"/>
-      <c r="J66" s="51"/>
-      <c r="K66" s="56"/>
-    </row>
-    <row r="67" ht="16.5" customHeight="1">
-      <c r="C67" s="51"/>
-      <c r="D67" s="51"/>
-      <c r="E67" s="51"/>
-      <c r="F67" s="51"/>
-      <c r="G67" s="51"/>
-      <c r="H67" s="51"/>
-      <c r="I67" s="51"/>
-      <c r="J67" s="51"/>
-      <c r="K67" s="56"/>
-    </row>
-    <row r="68" ht="16.5" customHeight="1">
-      <c r="C68" s="51"/>
-      <c r="D68" s="51"/>
-      <c r="E68" s="51"/>
-      <c r="F68" s="51"/>
-      <c r="G68" s="51"/>
-      <c r="H68" s="51"/>
-      <c r="I68" s="51"/>
-      <c r="J68" s="51"/>
-      <c r="K68" s="56"/>
-    </row>
-    <row r="69" ht="16.5" customHeight="1">
-      <c r="C69" s="51"/>
-      <c r="D69" s="51"/>
-      <c r="E69" s="51"/>
-      <c r="F69" s="51"/>
-      <c r="G69" s="51"/>
-      <c r="H69" s="51"/>
-      <c r="I69" s="51"/>
-      <c r="J69" s="51"/>
-      <c r="K69" s="56"/>
-    </row>
-    <row r="70" ht="16.5" customHeight="1">
-      <c r="C70" s="51"/>
-      <c r="D70" s="51"/>
-      <c r="E70" s="51"/>
-      <c r="F70" s="51"/>
-      <c r="G70" s="51"/>
-      <c r="H70" s="51"/>
-      <c r="I70" s="51"/>
-      <c r="J70" s="51"/>
-      <c r="K70" s="56"/>
-    </row>
-    <row r="71" ht="16.5" customHeight="1">
-      <c r="C71" s="51"/>
-      <c r="D71" s="51"/>
-      <c r="E71" s="51"/>
-      <c r="F71" s="51"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="51"/>
-      <c r="I71" s="51"/>
-      <c r="J71" s="51"/>
-      <c r="K71" s="56"/>
-    </row>
-    <row r="72" ht="16.5" customHeight="1">
-      <c r="C72" s="51"/>
-      <c r="D72" s="51"/>
-      <c r="E72" s="51"/>
-      <c r="F72" s="51"/>
-      <c r="G72" s="51"/>
-      <c r="H72" s="51"/>
-      <c r="I72" s="51"/>
-      <c r="J72" s="51"/>
-      <c r="K72" s="56"/>
-    </row>
-    <row r="73" ht="16.5" customHeight="1">
-      <c r="C73" s="51"/>
-      <c r="D73" s="51"/>
-      <c r="E73" s="51"/>
-      <c r="F73" s="51"/>
-      <c r="G73" s="51"/>
-      <c r="H73" s="51"/>
-      <c r="I73" s="51"/>
-      <c r="J73" s="51"/>
-      <c r="K73" s="56"/>
-    </row>
-    <row r="74" ht="16.5" customHeight="1">
-      <c r="C74" s="51"/>
-      <c r="D74" s="51"/>
-      <c r="E74" s="51"/>
-      <c r="F74" s="51"/>
-      <c r="G74" s="51"/>
-      <c r="H74" s="51"/>
-      <c r="I74" s="51"/>
-      <c r="J74" s="51"/>
-      <c r="K74" s="56"/>
-    </row>
-    <row r="75" ht="16.5" customHeight="1">
-      <c r="C75" s="51"/>
-      <c r="D75" s="51"/>
-      <c r="E75" s="51"/>
-      <c r="F75" s="51"/>
-      <c r="G75" s="51"/>
-      <c r="H75" s="51"/>
-      <c r="I75" s="51"/>
-      <c r="J75" s="51"/>
-      <c r="K75" s="56"/>
-    </row>
-    <row r="76" ht="16.5" customHeight="1">
-      <c r="C76" s="51"/>
-      <c r="D76" s="51"/>
-      <c r="E76" s="51"/>
-      <c r="F76" s="51"/>
-      <c r="G76" s="51"/>
-      <c r="H76" s="51"/>
-      <c r="I76" s="51"/>
-      <c r="J76" s="51"/>
-      <c r="K76" s="56"/>
-    </row>
-    <row r="77" ht="16.5" customHeight="1">
-      <c r="C77" s="51"/>
-      <c r="D77" s="51"/>
-      <c r="E77" s="51"/>
-      <c r="F77" s="51"/>
-      <c r="G77" s="51"/>
-      <c r="H77" s="51"/>
-      <c r="I77" s="51"/>
-      <c r="J77" s="51"/>
+      <c r="E63" s="50"/>
+      <c r="F63" s="50"/>
+      <c r="G63" s="50"/>
+      <c r="H63" s="50"/>
+      <c r="I63" s="50"/>
+      <c r="J63" s="50"/>
+      <c r="K63" s="52"/>
+      <c r="S63" s="5"/>
+    </row>
+    <row r="64" ht="16.5" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A64" s="53"/>
+      <c r="B64" s="53"/>
+      <c r="C64" s="50"/>
+      <c r="D64" s="50"/>
+      <c r="E64" s="50"/>
+      <c r="F64" s="50"/>
+      <c r="G64" s="50"/>
+      <c r="H64" s="50"/>
+      <c r="I64" s="50"/>
+      <c r="J64" s="50"/>
+      <c r="K64" s="54"/>
+      <c r="S64" s="5"/>
+    </row>
+    <row r="65" ht="16.5" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A65" s="55"/>
+      <c r="B65" s="55"/>
+      <c r="C65" s="50"/>
+      <c r="D65" s="50"/>
+      <c r="E65" s="50"/>
+      <c r="F65" s="50"/>
+      <c r="G65" s="50"/>
+      <c r="H65" s="50"/>
+      <c r="I65" s="50"/>
+      <c r="J65" s="50"/>
+      <c r="K65" s="54"/>
+      <c r="S65" s="5"/>
+    </row>
+    <row r="66" ht="16.5" customHeight="1" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C66" s="50"/>
+      <c r="D66" s="50"/>
+      <c r="E66" s="50"/>
+      <c r="F66" s="50"/>
+      <c r="G66" s="50"/>
+      <c r="H66" s="50"/>
+      <c r="I66" s="50"/>
+      <c r="J66" s="50"/>
+      <c r="K66" s="54"/>
+      <c r="S66" s="5"/>
+    </row>
+    <row r="67" ht="16.5" customHeight="1" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C67" s="50"/>
+      <c r="D67" s="50"/>
+      <c r="E67" s="50"/>
+      <c r="F67" s="50"/>
+      <c r="G67" s="50"/>
+      <c r="H67" s="50"/>
+      <c r="I67" s="50"/>
+      <c r="J67" s="50"/>
+      <c r="K67" s="54"/>
+      <c r="S67" s="5"/>
+    </row>
+    <row r="68" ht="16.5" customHeight="1" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C68" s="50"/>
+      <c r="D68" s="50"/>
+      <c r="E68" s="50"/>
+      <c r="F68" s="50"/>
+      <c r="G68" s="50"/>
+      <c r="H68" s="50"/>
+      <c r="I68" s="50"/>
+      <c r="J68" s="50"/>
+      <c r="K68" s="54"/>
+      <c r="S68" s="5"/>
+    </row>
+    <row r="69" ht="16.5" customHeight="1" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C69" s="50"/>
+      <c r="D69" s="50"/>
+      <c r="E69" s="50"/>
+      <c r="F69" s="50"/>
+      <c r="G69" s="50"/>
+      <c r="H69" s="50"/>
+      <c r="I69" s="50"/>
+      <c r="J69" s="50"/>
+      <c r="K69" s="54"/>
+      <c r="S69" s="5"/>
+    </row>
+    <row r="70" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C70" s="50"/>
+      <c r="D70" s="50"/>
+      <c r="E70" s="50"/>
+      <c r="F70" s="50"/>
+      <c r="G70" s="50"/>
+      <c r="H70" s="50"/>
+      <c r="I70" s="50"/>
+      <c r="J70" s="50"/>
+      <c r="K70" s="54"/>
+    </row>
+    <row r="71" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C71" s="50"/>
+      <c r="D71" s="50"/>
+      <c r="E71" s="50"/>
+      <c r="F71" s="50"/>
+      <c r="G71" s="50"/>
+      <c r="H71" s="50"/>
+      <c r="I71" s="50"/>
+      <c r="J71" s="50"/>
+      <c r="K71" s="54"/>
+    </row>
+    <row r="72" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C72" s="50"/>
+      <c r="D72" s="50"/>
+      <c r="E72" s="50"/>
+      <c r="F72" s="50"/>
+      <c r="G72" s="50"/>
+      <c r="H72" s="50"/>
+      <c r="I72" s="50"/>
+      <c r="J72" s="50"/>
+      <c r="K72" s="54"/>
+    </row>
+    <row r="73" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C73" s="50"/>
+      <c r="D73" s="50"/>
+      <c r="E73" s="50"/>
+      <c r="F73" s="50"/>
+      <c r="G73" s="50"/>
+      <c r="H73" s="50"/>
+      <c r="I73" s="50"/>
+      <c r="J73" s="50"/>
+      <c r="K73" s="54"/>
+    </row>
+    <row r="74" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C74" s="50"/>
+      <c r="D74" s="50"/>
+      <c r="E74" s="50"/>
+      <c r="F74" s="50"/>
+      <c r="G74" s="50"/>
+      <c r="H74" s="50"/>
+      <c r="I74" s="50"/>
+      <c r="J74" s="50"/>
+      <c r="K74" s="54"/>
+    </row>
+    <row r="75" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C75" s="50"/>
+      <c r="D75" s="50"/>
+      <c r="E75" s="50"/>
+      <c r="F75" s="50"/>
+      <c r="G75" s="50"/>
+      <c r="H75" s="50"/>
+      <c r="I75" s="50"/>
+      <c r="J75" s="50"/>
+      <c r="K75" s="54"/>
+    </row>
+    <row r="76" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C76" s="50"/>
+      <c r="D76" s="50"/>
+      <c r="E76" s="50"/>
+      <c r="F76" s="50"/>
+      <c r="G76" s="50"/>
+      <c r="H76" s="50"/>
+      <c r="I76" s="50"/>
+      <c r="J76" s="50"/>
+      <c r="K76" s="54"/>
+    </row>
+    <row r="77" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C77" s="50"/>
+      <c r="D77" s="50"/>
+      <c r="E77" s="50"/>
+      <c r="F77" s="50"/>
+      <c r="G77" s="50"/>
+      <c r="H77" s="50"/>
+      <c r="I77" s="50"/>
+      <c r="J77" s="50"/>
       <c r="K77" s="54"/>
     </row>
-    <row r="78" ht="16.5" customHeight="1">
-      <c r="C78" s="51"/>
-      <c r="D78" s="51"/>
-      <c r="E78" s="51"/>
-      <c r="F78" s="51"/>
-      <c r="G78" s="51"/>
-      <c r="H78" s="51"/>
-      <c r="I78" s="51"/>
-      <c r="J78" s="51"/>
+    <row r="78" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C78" s="50"/>
+      <c r="D78" s="50"/>
+      <c r="E78" s="50"/>
+      <c r="F78" s="50"/>
+      <c r="G78" s="50"/>
+      <c r="H78" s="50"/>
+      <c r="I78" s="50"/>
+      <c r="J78" s="50"/>
       <c r="K78" s="54"/>
     </row>
-    <row r="79" ht="16.5" customHeight="1">
-      <c r="C79" s="51"/>
-      <c r="D79" s="51"/>
-      <c r="E79" s="51"/>
-      <c r="F79" s="51"/>
-      <c r="G79" s="51"/>
-      <c r="H79" s="51"/>
-      <c r="I79" s="51"/>
-      <c r="J79" s="51"/>
+    <row r="79" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C79" s="50"/>
+      <c r="D79" s="50"/>
+      <c r="E79" s="50"/>
+      <c r="F79" s="50"/>
+      <c r="G79" s="50"/>
+      <c r="H79" s="50"/>
+      <c r="I79" s="50"/>
+      <c r="J79" s="50"/>
       <c r="K79" s="54"/>
     </row>
-    <row r="80" ht="16.5" customHeight="1">
-      <c r="C80" s="51"/>
-      <c r="D80" s="51"/>
-      <c r="E80" s="51"/>
-      <c r="F80" s="51"/>
-      <c r="G80" s="51"/>
-      <c r="H80" s="51"/>
-      <c r="I80" s="51"/>
-      <c r="J80" s="51"/>
-      <c r="K80" s="56"/>
-    </row>
-    <row r="81" ht="16.5" customHeight="1">
-      <c r="C81" s="51"/>
-      <c r="D81" s="51"/>
-      <c r="E81" s="51"/>
-      <c r="F81" s="51"/>
-      <c r="G81" s="51"/>
-      <c r="H81" s="51"/>
-      <c r="I81" s="51"/>
-      <c r="J81" s="51"/>
-      <c r="K81" s="56"/>
-    </row>
-    <row r="82" ht="16.5" customHeight="1">
-      <c r="C82" s="51"/>
-      <c r="D82" s="51"/>
-      <c r="E82" s="51"/>
-      <c r="F82" s="51"/>
-      <c r="G82" s="51"/>
-      <c r="H82" s="51"/>
-      <c r="I82" s="51"/>
-      <c r="J82" s="51"/>
-      <c r="K82" s="56"/>
-    </row>
-    <row r="83" ht="16.5" customHeight="1">
-      <c r="C83" s="51"/>
-      <c r="D83" s="51"/>
-      <c r="E83" s="51"/>
-      <c r="F83" s="51"/>
-      <c r="G83" s="51"/>
-      <c r="H83" s="51"/>
-      <c r="I83" s="51"/>
-      <c r="J83" s="51"/>
-      <c r="K83" s="56"/>
-    </row>
-    <row r="84" ht="16.5" customHeight="1">
-      <c r="C84" s="51"/>
-      <c r="D84" s="51"/>
-      <c r="E84" s="51"/>
-      <c r="F84" s="51"/>
-      <c r="G84" s="51"/>
-      <c r="H84" s="51"/>
-      <c r="I84" s="51"/>
-      <c r="J84" s="51"/>
-      <c r="K84" s="56"/>
-    </row>
-    <row r="85" ht="16.5" customHeight="1">
-      <c r="C85" s="51"/>
-      <c r="D85" s="51"/>
-      <c r="E85" s="51"/>
-      <c r="F85" s="51"/>
-      <c r="G85" s="51"/>
-      <c r="H85" s="51"/>
-      <c r="I85" s="51"/>
-      <c r="J85" s="51"/>
+    <row r="80" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C80" s="50"/>
+      <c r="D80" s="50"/>
+      <c r="E80" s="50"/>
+      <c r="F80" s="50"/>
+      <c r="G80" s="50"/>
+      <c r="H80" s="50"/>
+      <c r="I80" s="50"/>
+      <c r="J80" s="50"/>
+      <c r="K80" s="54"/>
+    </row>
+    <row r="81" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C81" s="50"/>
+      <c r="D81" s="50"/>
+      <c r="E81" s="50"/>
+      <c r="F81" s="50"/>
+      <c r="G81" s="50"/>
+      <c r="H81" s="50"/>
+      <c r="I81" s="50"/>
+      <c r="J81" s="50"/>
+      <c r="K81" s="54"/>
+    </row>
+    <row r="82" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C82" s="50"/>
+      <c r="D82" s="50"/>
+      <c r="E82" s="50"/>
+      <c r="F82" s="50"/>
+      <c r="G82" s="50"/>
+      <c r="H82" s="50"/>
+      <c r="I82" s="50"/>
+      <c r="J82" s="50"/>
+      <c r="K82" s="54"/>
+    </row>
+    <row r="83" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C83" s="50"/>
+      <c r="D83" s="50"/>
+      <c r="E83" s="50"/>
+      <c r="F83" s="50"/>
+      <c r="G83" s="50"/>
+      <c r="H83" s="50"/>
+      <c r="I83" s="50"/>
+      <c r="J83" s="50"/>
+      <c r="K83" s="54"/>
+    </row>
+    <row r="84" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C84" s="50"/>
+      <c r="D84" s="50"/>
+      <c r="E84" s="50"/>
+      <c r="F84" s="50"/>
+      <c r="G84" s="50"/>
+      <c r="H84" s="50"/>
+      <c r="I84" s="50"/>
+      <c r="J84" s="50"/>
+      <c r="K84" s="54"/>
+    </row>
+    <row r="85" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C85" s="50"/>
+      <c r="D85" s="50"/>
+      <c r="E85" s="50"/>
+      <c r="F85" s="50"/>
+      <c r="G85" s="50"/>
+      <c r="H85" s="50"/>
+      <c r="I85" s="50"/>
+      <c r="J85" s="50"/>
       <c r="K85" s="54"/>
     </row>
-    <row r="86" ht="16.5" customHeight="1">
-      <c r="C86" s="51"/>
-      <c r="D86" s="51"/>
-      <c r="E86" s="51"/>
-      <c r="F86" s="51"/>
-      <c r="G86" s="51"/>
-      <c r="H86" s="51"/>
-      <c r="I86" s="51"/>
-      <c r="J86" s="51"/>
+    <row r="86" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C86" s="50"/>
+      <c r="D86" s="50"/>
+      <c r="E86" s="50"/>
+      <c r="F86" s="50"/>
+      <c r="G86" s="50"/>
+      <c r="H86" s="50"/>
+      <c r="I86" s="50"/>
+      <c r="J86" s="50"/>
       <c r="K86" s="54"/>
     </row>
-    <row r="87" ht="16.5" customHeight="1">
-      <c r="C87" s="51"/>
-      <c r="D87" s="51"/>
-      <c r="E87" s="51"/>
-      <c r="F87" s="51"/>
-      <c r="G87" s="51"/>
-      <c r="H87" s="51"/>
-      <c r="I87" s="51"/>
-      <c r="J87" s="51"/>
+    <row r="87" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C87" s="50"/>
+      <c r="D87" s="50"/>
+      <c r="E87" s="50"/>
+      <c r="F87" s="50"/>
+      <c r="G87" s="50"/>
+      <c r="H87" s="50"/>
+      <c r="I87" s="50"/>
+      <c r="J87" s="50"/>
       <c r="K87" s="54"/>
     </row>
-    <row r="88" ht="16.5" customHeight="1">
-      <c r="C88" s="51"/>
-      <c r="D88" s="51"/>
-      <c r="E88" s="51"/>
-      <c r="F88" s="51"/>
-      <c r="G88" s="51"/>
-      <c r="H88" s="51"/>
-      <c r="I88" s="51"/>
-      <c r="J88" s="51"/>
+    <row r="88" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C88" s="50"/>
+      <c r="D88" s="50"/>
+      <c r="E88" s="50"/>
+      <c r="F88" s="50"/>
+      <c r="G88" s="50"/>
+      <c r="H88" s="50"/>
+      <c r="I88" s="50"/>
+      <c r="J88" s="50"/>
       <c r="K88" s="54"/>
     </row>
-    <row r="89" ht="16.5" customHeight="1">
-      <c r="C89" s="51"/>
-      <c r="D89" s="51"/>
-      <c r="E89" s="51"/>
-      <c r="F89" s="51"/>
-      <c r="G89" s="51"/>
-      <c r="H89" s="51"/>
-      <c r="I89" s="51"/>
-      <c r="J89" s="51"/>
+    <row r="89" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C89" s="50"/>
+      <c r="D89" s="50"/>
+      <c r="E89" s="50"/>
+      <c r="F89" s="50"/>
+      <c r="G89" s="50"/>
+      <c r="H89" s="50"/>
+      <c r="I89" s="50"/>
+      <c r="J89" s="50"/>
       <c r="K89" s="54"/>
     </row>
-    <row r="90" ht="16.5" customHeight="1">
-      <c r="C90" s="51"/>
-      <c r="D90" s="51"/>
-      <c r="E90" s="51"/>
-      <c r="F90" s="51"/>
-      <c r="G90" s="51"/>
-      <c r="H90" s="51"/>
-      <c r="I90" s="51"/>
-      <c r="J90" s="51"/>
+    <row r="90" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C90" s="50"/>
+      <c r="D90" s="50"/>
+      <c r="E90" s="50"/>
+      <c r="F90" s="50"/>
+      <c r="G90" s="50"/>
+      <c r="H90" s="50"/>
+      <c r="I90" s="50"/>
+      <c r="J90" s="50"/>
       <c r="K90" s="54"/>
     </row>
-    <row r="91" ht="16.5" customHeight="1">
-      <c r="C91" s="51"/>
-      <c r="D91" s="51"/>
-      <c r="E91" s="51"/>
-      <c r="F91" s="51"/>
-      <c r="G91" s="51"/>
-      <c r="H91" s="51"/>
-      <c r="I91" s="51"/>
-      <c r="J91" s="51"/>
-      <c r="K91" s="54"/>
-    </row>
-    <row r="92" ht="16.5" customHeight="1">
-      <c r="C92" s="51"/>
-      <c r="D92" s="51"/>
-      <c r="E92" s="51"/>
-      <c r="F92" s="51"/>
-      <c r="G92" s="51"/>
-      <c r="H92" s="51"/>
-      <c r="I92" s="51"/>
-      <c r="J92" s="51"/>
-      <c r="K92" s="54"/>
-    </row>
-    <row r="93" ht="16.5" customHeight="1">
-      <c r="C93" s="51"/>
-      <c r="D93" s="51"/>
-      <c r="E93" s="51"/>
-      <c r="F93" s="51"/>
-      <c r="G93" s="51"/>
-      <c r="H93" s="51"/>
-      <c r="I93" s="51"/>
-      <c r="J93" s="51"/>
-      <c r="K93" s="54"/>
-    </row>
-    <row r="94" ht="16.5" customHeight="1">
-      <c r="C94" s="51"/>
-      <c r="D94" s="51"/>
-      <c r="E94" s="51"/>
-      <c r="F94" s="51"/>
-      <c r="G94" s="51"/>
-      <c r="H94" s="51"/>
-      <c r="I94" s="51"/>
-      <c r="J94" s="51"/>
+    <row r="91" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C91" s="50"/>
+      <c r="D91" s="50"/>
+      <c r="E91" s="50"/>
+      <c r="F91" s="50"/>
+      <c r="G91" s="50"/>
+      <c r="H91" s="50"/>
+      <c r="I91" s="50"/>
+      <c r="J91" s="50"/>
+      <c r="K91" s="52"/>
+    </row>
+    <row r="92" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C92" s="50"/>
+      <c r="D92" s="50"/>
+      <c r="E92" s="50"/>
+      <c r="F92" s="50"/>
+      <c r="G92" s="50"/>
+      <c r="H92" s="50"/>
+      <c r="I92" s="50"/>
+      <c r="J92" s="50"/>
+      <c r="K92" s="52"/>
+    </row>
+    <row r="93" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C93" s="50"/>
+      <c r="D93" s="50"/>
+      <c r="E93" s="50"/>
+      <c r="F93" s="50"/>
+      <c r="G93" s="50"/>
+      <c r="H93" s="50"/>
+      <c r="I93" s="50"/>
+      <c r="J93" s="50"/>
+      <c r="K93" s="52"/>
+    </row>
+    <row r="94" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C94" s="50"/>
+      <c r="D94" s="50"/>
+      <c r="E94" s="50"/>
+      <c r="F94" s="50"/>
+      <c r="G94" s="50"/>
+      <c r="H94" s="50"/>
+      <c r="I94" s="50"/>
+      <c r="J94" s="50"/>
       <c r="K94" s="54"/>
     </row>
-    <row r="95" ht="16.5" customHeight="1">
-      <c r="C95" s="51"/>
-      <c r="D95" s="51"/>
-      <c r="E95" s="51"/>
-      <c r="F95" s="51"/>
-      <c r="G95" s="51"/>
-      <c r="H95" s="51"/>
-      <c r="I95" s="51"/>
-      <c r="J95" s="51"/>
+    <row r="95" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C95" s="50"/>
+      <c r="D95" s="50"/>
+      <c r="E95" s="50"/>
+      <c r="F95" s="50"/>
+      <c r="G95" s="50"/>
+      <c r="H95" s="50"/>
+      <c r="I95" s="50"/>
+      <c r="J95" s="50"/>
       <c r="K95" s="54"/>
     </row>
-    <row r="96" ht="16.5" customHeight="1">
-      <c r="C96" s="51"/>
-      <c r="D96" s="51"/>
-      <c r="E96" s="51"/>
-      <c r="F96" s="51"/>
-      <c r="G96" s="51"/>
-      <c r="H96" s="51"/>
-      <c r="I96" s="51"/>
-      <c r="J96" s="51"/>
+    <row r="96" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C96" s="50"/>
+      <c r="D96" s="50"/>
+      <c r="E96" s="50"/>
+      <c r="F96" s="50"/>
+      <c r="G96" s="50"/>
+      <c r="H96" s="50"/>
+      <c r="I96" s="50"/>
+      <c r="J96" s="50"/>
       <c r="K96" s="54"/>
     </row>
-    <row r="97" ht="16.5" customHeight="1">
-      <c r="C97" s="51"/>
-      <c r="D97" s="51"/>
-      <c r="E97" s="51"/>
-      <c r="F97" s="51"/>
-      <c r="G97" s="51"/>
-      <c r="H97" s="51"/>
-      <c r="I97" s="51"/>
-      <c r="J97" s="51"/>
+    <row r="97" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C97" s="50"/>
+      <c r="D97" s="50"/>
+      <c r="E97" s="50"/>
+      <c r="F97" s="50"/>
+      <c r="G97" s="50"/>
+      <c r="H97" s="50"/>
+      <c r="I97" s="50"/>
+      <c r="J97" s="50"/>
       <c r="K97" s="54"/>
     </row>
-    <row r="98" ht="16.5" customHeight="1">
-      <c r="C98" s="51"/>
-      <c r="D98" s="51"/>
-      <c r="E98" s="51"/>
-      <c r="F98" s="51"/>
-      <c r="G98" s="51"/>
-      <c r="H98" s="51"/>
-      <c r="I98" s="51"/>
-      <c r="J98" s="51"/>
+    <row r="98" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C98" s="50"/>
+      <c r="D98" s="50"/>
+      <c r="E98" s="50"/>
+      <c r="F98" s="50"/>
+      <c r="G98" s="50"/>
+      <c r="H98" s="50"/>
+      <c r="I98" s="50"/>
+      <c r="J98" s="50"/>
       <c r="K98" s="54"/>
     </row>
-    <row r="99" ht="16.5" customHeight="1">
-      <c r="C99" s="49"/>
-      <c r="D99" s="49"/>
-      <c r="E99" s="49"/>
-      <c r="F99" s="49"/>
-      <c r="G99" s="49"/>
-      <c r="H99" s="49"/>
-      <c r="I99" s="49"/>
-      <c r="J99" s="49"/>
-      <c r="K99" s="49"/>
-    </row>
-    <row r="100" ht="16.5" customHeight="1">
-      <c r="C100" s="49"/>
-      <c r="D100" s="49"/>
-      <c r="E100" s="49"/>
-      <c r="F100" s="49"/>
-      <c r="G100" s="49"/>
-      <c r="H100" s="49"/>
-      <c r="I100" s="49"/>
-      <c r="J100" s="49"/>
-      <c r="K100" s="49"/>
-    </row>
-    <row r="101" ht="16.5" customHeight="1">
-      <c r="C101" s="49"/>
-      <c r="D101" s="49"/>
-      <c r="E101" s="49"/>
-      <c r="F101" s="49"/>
-      <c r="G101" s="49"/>
-      <c r="H101" s="49"/>
-      <c r="I101" s="49"/>
-      <c r="J101" s="49"/>
-      <c r="K101" s="49"/>
-    </row>
-    <row r="102" ht="16.5" customHeight="1">
-      <c r="C102" s="49"/>
-      <c r="D102" s="49"/>
-      <c r="E102" s="49"/>
-      <c r="F102" s="49"/>
-      <c r="G102" s="49"/>
-      <c r="H102" s="49"/>
-      <c r="I102" s="49"/>
-      <c r="J102" s="49"/>
-      <c r="K102" s="49"/>
-    </row>
-    <row r="103" ht="16.5" customHeight="1">
-      <c r="C103" s="49"/>
-      <c r="D103" s="49"/>
-      <c r="E103" s="49"/>
-      <c r="F103" s="49"/>
-      <c r="G103" s="49"/>
-      <c r="H103" s="49"/>
-      <c r="I103" s="49"/>
-      <c r="J103" s="49"/>
-      <c r="K103" s="49"/>
-    </row>
-    <row r="104" ht="16.5" customHeight="1">
-      <c r="C104" s="49"/>
-      <c r="D104" s="49"/>
-      <c r="E104" s="49"/>
-      <c r="F104" s="49"/>
-      <c r="G104" s="49"/>
-      <c r="H104" s="49"/>
-      <c r="I104" s="49"/>
-      <c r="J104" s="49"/>
-      <c r="K104" s="49"/>
-    </row>
-    <row r="105" ht="16.5" customHeight="1">
-      <c r="C105" s="49"/>
-      <c r="D105" s="49"/>
-      <c r="E105" s="49"/>
-      <c r="F105" s="49"/>
-      <c r="G105" s="49"/>
-      <c r="H105" s="49"/>
-      <c r="I105" s="49"/>
-      <c r="J105" s="49"/>
-      <c r="K105" s="49"/>
-    </row>
-    <row r="106" ht="16.5" customHeight="1">
-      <c r="C106" s="49"/>
-      <c r="D106" s="49"/>
-      <c r="E106" s="49"/>
-      <c r="F106" s="49"/>
-      <c r="G106" s="49"/>
-      <c r="H106" s="49"/>
-      <c r="I106" s="49"/>
-      <c r="J106" s="49"/>
-      <c r="K106" s="49"/>
-    </row>
-    <row r="107" ht="16.5" customHeight="1">
-      <c r="C107" s="49"/>
-      <c r="D107" s="49"/>
-      <c r="E107" s="49"/>
-      <c r="F107" s="49"/>
-      <c r="G107" s="49"/>
-      <c r="H107" s="49"/>
-      <c r="I107" s="49"/>
-      <c r="J107" s="49"/>
-      <c r="K107" s="49"/>
-    </row>
-    <row r="108" ht="16.5" customHeight="1">
-      <c r="C108" s="49"/>
-      <c r="D108" s="49"/>
-      <c r="E108" s="49"/>
-      <c r="F108" s="49"/>
-      <c r="G108" s="49"/>
-      <c r="H108" s="49"/>
-      <c r="I108" s="49"/>
-      <c r="J108" s="49"/>
-      <c r="K108" s="49"/>
-    </row>
-    <row r="109" ht="16.5" customHeight="1"/>
-    <row r="110" ht="16.5" customHeight="1"/>
-    <row r="111" ht="16.5" customHeight="1"/>
-    <row r="112" ht="16.5" customHeight="1"/>
-    <row r="113" ht="16.5" customHeight="1"/>
-    <row r="114" ht="16.5" customHeight="1"/>
-    <row r="115" ht="16.5" customHeight="1"/>
-    <row r="116" ht="16.5" customHeight="1"/>
-    <row r="117" ht="16.5" customHeight="1"/>
-    <row r="118" ht="16.5" customHeight="1"/>
-    <row r="119" ht="16.5" customHeight="1"/>
-    <row r="120" ht="16.5" customHeight="1"/>
-    <row r="121" ht="16.5" customHeight="1"/>
-    <row r="122" ht="16.5" customHeight="1"/>
-    <row r="123" ht="16.5" customHeight="1"/>
-    <row r="124" ht="16.5" customHeight="1"/>
-    <row r="125" ht="16.5" customHeight="1"/>
-    <row r="126" ht="16.5" customHeight="1"/>
-    <row r="127" ht="16.5" customHeight="1"/>
-    <row r="128" ht="16.5" customHeight="1"/>
-    <row r="129" ht="16.5" customHeight="1"/>
-    <row r="130" ht="16.5" customHeight="1"/>
-    <row r="131" ht="16.5" customHeight="1"/>
-    <row r="132" ht="16.5" customHeight="1"/>
-    <row r="133" ht="16.5" customHeight="1"/>
-    <row r="134" ht="16.5" customHeight="1"/>
-    <row r="135" ht="16.5" customHeight="1"/>
-    <row r="136" ht="16.5" customHeight="1"/>
-    <row r="137" ht="16.5" customHeight="1"/>
-    <row r="138" ht="16.5" customHeight="1"/>
-    <row r="139" ht="16.5" customHeight="1"/>
-    <row r="140" ht="16.5" customHeight="1"/>
-    <row r="141" ht="16.5" customHeight="1"/>
-    <row r="142" ht="16.5" customHeight="1"/>
-    <row r="143" ht="16.5" customHeight="1"/>
-    <row r="144" ht="16.5" customHeight="1"/>
-    <row r="145" ht="16.5" customHeight="1"/>
-    <row r="146" ht="16.5" customHeight="1"/>
-    <row r="147" ht="16.5" customHeight="1"/>
-    <row r="148" ht="16.5" customHeight="1"/>
-    <row r="149" ht="16.5" customHeight="1"/>
-    <row r="150" ht="16.5" customHeight="1"/>
-    <row r="151" ht="16.5" customHeight="1"/>
-    <row r="152" ht="16.5" customHeight="1"/>
-    <row r="153" ht="16.5" customHeight="1"/>
-    <row r="154" ht="16.5" customHeight="1"/>
-    <row r="155" ht="16.5" customHeight="1"/>
-    <row r="156" ht="16.5" customHeight="1"/>
-    <row r="157" ht="16.5" customHeight="1"/>
-    <row r="158" ht="16.5" customHeight="1"/>
-    <row r="159" ht="16.5" customHeight="1"/>
-    <row r="160" ht="16.5" customHeight="1"/>
-    <row r="161" ht="16.5" customHeight="1"/>
-    <row r="162" ht="16.5" customHeight="1"/>
-    <row r="163" ht="16.5" customHeight="1"/>
-    <row r="164" ht="16.5" customHeight="1"/>
-    <row r="165" ht="16.5" customHeight="1"/>
-    <row r="166" ht="16.5" customHeight="1"/>
-    <row r="167" ht="16.5" customHeight="1"/>
-    <row r="168" ht="16.5" customHeight="1"/>
-    <row r="169" ht="16.5" customHeight="1"/>
-    <row r="170" ht="16.5" customHeight="1"/>
-    <row r="171" ht="16.5" customHeight="1"/>
-    <row r="172" ht="16.5" customHeight="1"/>
-    <row r="173" ht="16.5" customHeight="1"/>
-    <row r="174" ht="16.5" customHeight="1"/>
-    <row r="175" ht="16.5" customHeight="1"/>
-    <row r="176" ht="16.5" customHeight="1"/>
-    <row r="177" ht="16.5" customHeight="1"/>
-    <row r="178" ht="16.5" customHeight="1"/>
-    <row r="179" ht="16.5" customHeight="1"/>
-    <row r="180" ht="16.5" customHeight="1"/>
-    <row r="181" ht="16.5" customHeight="1"/>
-    <row r="182" ht="16.5" customHeight="1"/>
-    <row r="183" ht="16.5" customHeight="1"/>
-    <row r="184" ht="16.5" customHeight="1"/>
-    <row r="185" ht="16.5" customHeight="1"/>
-    <row r="186" ht="16.5" customHeight="1"/>
-    <row r="187" ht="16.5" customHeight="1"/>
-    <row r="188" ht="16.5" customHeight="1"/>
-    <row r="189" ht="16.5" customHeight="1"/>
-    <row r="190" ht="16.5" customHeight="1"/>
-    <row r="191" ht="16.5" customHeight="1"/>
-    <row r="192" ht="16.5" customHeight="1"/>
-    <row r="193" ht="16.5" customHeight="1"/>
-    <row r="194" ht="16.5" customHeight="1"/>
-    <row r="195" ht="16.5" customHeight="1"/>
-    <row r="196" ht="16.5" customHeight="1"/>
-    <row r="197" ht="16.5" customHeight="1"/>
-    <row r="198" ht="16.5" customHeight="1"/>
-    <row r="199" ht="16.5" customHeight="1"/>
-    <row r="200" ht="16.5" customHeight="1"/>
-    <row r="201" ht="16.5" customHeight="1"/>
-    <row r="202" ht="16.5" customHeight="1"/>
-    <row r="203" ht="16.5" customHeight="1"/>
-    <row r="204" ht="16.5" customHeight="1"/>
-    <row r="205" ht="16.5" customHeight="1"/>
-    <row r="206" ht="16.5" customHeight="1"/>
-    <row r="207" ht="16.5" customHeight="1"/>
-    <row r="208" ht="16.5" customHeight="1"/>
-    <row r="209" ht="16.5" customHeight="1"/>
-    <row r="210" ht="16.5" customHeight="1"/>
-    <row r="211" ht="16.5" customHeight="1"/>
-    <row r="212" ht="16.5" customHeight="1"/>
-    <row r="213" ht="16.5" customHeight="1"/>
-    <row r="214" ht="16.5" customHeight="1"/>
-    <row r="215" ht="16.5" customHeight="1"/>
-    <row r="216" ht="16.5" customHeight="1"/>
-    <row r="217" ht="16.5" customHeight="1"/>
-    <row r="218" ht="16.5" customHeight="1"/>
-    <row r="219" ht="16.5" customHeight="1"/>
-    <row r="220" ht="16.5" customHeight="1"/>
-    <row r="221" ht="16.5" customHeight="1"/>
-    <row r="222" ht="16.5" customHeight="1"/>
-    <row r="223" ht="16.5" customHeight="1"/>
-    <row r="224" ht="16.5" customHeight="1"/>
-    <row r="225" ht="16.5" customHeight="1"/>
-    <row r="226" ht="16.5" customHeight="1"/>
-    <row r="227" ht="16.5" customHeight="1"/>
-    <row r="228" ht="16.5" customHeight="1"/>
-    <row r="229" ht="16.5" customHeight="1"/>
-    <row r="230" ht="16.5" customHeight="1"/>
-    <row r="231" ht="16.5" customHeight="1"/>
-    <row r="232" ht="16.5" customHeight="1"/>
-    <row r="233" ht="16.5" customHeight="1"/>
-    <row r="234" ht="16.5" customHeight="1"/>
-    <row r="235" ht="16.5" customHeight="1"/>
-    <row r="236" ht="16.5" customHeight="1"/>
-    <row r="237" ht="16.5" customHeight="1"/>
-    <row r="238" ht="16.5" customHeight="1"/>
-    <row r="239" ht="16.5" customHeight="1"/>
-    <row r="240" ht="16.5" customHeight="1"/>
-    <row r="241" ht="16.5" customHeight="1"/>
-    <row r="242" ht="16.5" customHeight="1"/>
-    <row r="243" ht="16.5" customHeight="1"/>
-    <row r="244" ht="16.5" customHeight="1"/>
-    <row r="245" ht="16.5" customHeight="1"/>
-    <row r="246" ht="16.5" customHeight="1"/>
-    <row r="247" ht="16.5" customHeight="1"/>
-    <row r="248" ht="16.5" customHeight="1"/>
-    <row r="249" ht="16.5" customHeight="1"/>
-    <row r="250" ht="16.5" customHeight="1"/>
-    <row r="251" ht="16.5" customHeight="1"/>
-    <row r="252" ht="16.5" customHeight="1"/>
-    <row r="253" ht="16.5" customHeight="1"/>
-    <row r="254" ht="16.5" customHeight="1"/>
-    <row r="255" ht="16.5" customHeight="1"/>
-    <row r="256" ht="16.5" customHeight="1"/>
-    <row r="257" ht="16.5" customHeight="1"/>
-    <row r="258" ht="16.5" customHeight="1"/>
-    <row r="259" ht="16.5" customHeight="1"/>
-    <row r="260" ht="16.5" customHeight="1"/>
-    <row r="261" ht="16.5" customHeight="1"/>
-    <row r="262" ht="16.5" customHeight="1"/>
-    <row r="263" ht="16.5" customHeight="1"/>
-    <row r="264" ht="16.5" customHeight="1"/>
-    <row r="265" ht="16.5" customHeight="1"/>
-    <row r="266" ht="16.5" customHeight="1"/>
-    <row r="267" ht="16.5" customHeight="1"/>
-    <row r="268" ht="16.5" customHeight="1"/>
-    <row r="269" ht="16.5" customHeight="1"/>
-    <row r="270" ht="16.5" customHeight="1"/>
-    <row r="271" ht="16.5" customHeight="1"/>
-    <row r="272" ht="16.5" customHeight="1"/>
-    <row r="273" ht="16.5" customHeight="1"/>
-    <row r="274" ht="16.5" customHeight="1"/>
-    <row r="275" ht="16.5" customHeight="1"/>
-    <row r="276" ht="16.5" customHeight="1"/>
-    <row r="277" ht="16.5" customHeight="1"/>
-    <row r="278" ht="16.5" customHeight="1"/>
-    <row r="279" ht="16.5" customHeight="1"/>
-    <row r="280" ht="16.5" customHeight="1"/>
-    <row r="281" ht="16.5" customHeight="1"/>
-    <row r="282" ht="16.5" customHeight="1"/>
-    <row r="283" ht="16.5" customHeight="1"/>
-    <row r="284" ht="16.5" customHeight="1"/>
-    <row r="285" ht="16.5" customHeight="1"/>
-    <row r="286" ht="16.5" customHeight="1"/>
-    <row r="287" ht="16.5" customHeight="1"/>
-    <row r="288" ht="16.5" customHeight="1"/>
-    <row r="289" ht="16.5" customHeight="1"/>
-    <row r="290" ht="16.5" customHeight="1"/>
-    <row r="291" ht="16.5" customHeight="1"/>
-    <row r="292" ht="16.5" customHeight="1"/>
-    <row r="293" ht="16.5" customHeight="1"/>
-    <row r="294" ht="16.5" customHeight="1"/>
-    <row r="295" ht="16.5" customHeight="1"/>
-    <row r="296" ht="16.5" customHeight="1"/>
-    <row r="297" ht="16.5" customHeight="1"/>
-    <row r="298" ht="16.5" customHeight="1"/>
-    <row r="299" ht="16.5" customHeight="1"/>
-    <row r="300" ht="16.5" customHeight="1"/>
-    <row r="301" ht="16.5" customHeight="1"/>
-    <row r="302" ht="16.5" customHeight="1"/>
-    <row r="303" ht="16.5" customHeight="1"/>
-    <row r="304" ht="16.5" customHeight="1"/>
-    <row r="305" ht="16.5" customHeight="1"/>
-    <row r="306" ht="16.5" customHeight="1"/>
-    <row r="307" ht="16.5" customHeight="1"/>
-    <row r="308" ht="16.5" customHeight="1"/>
-    <row r="309" ht="16.5" customHeight="1"/>
-    <row r="310" ht="16.5" customHeight="1"/>
-    <row r="311" ht="16.5" customHeight="1"/>
-    <row r="312" ht="16.5" customHeight="1"/>
-    <row r="313" ht="16.5" customHeight="1"/>
-    <row r="314" ht="16.5" customHeight="1"/>
-    <row r="315" ht="16.5" customHeight="1"/>
-    <row r="316" ht="16.5" customHeight="1"/>
-    <row r="317" ht="16.5" customHeight="1"/>
-    <row r="318" ht="16.5" customHeight="1"/>
-    <row r="319" ht="16.5" customHeight="1"/>
-    <row r="320" ht="16.5" customHeight="1"/>
-    <row r="321" ht="16.5" customHeight="1"/>
-    <row r="322" ht="16.5" customHeight="1"/>
-    <row r="323" ht="16.5" customHeight="1"/>
-    <row r="324" ht="16.5" customHeight="1"/>
-    <row r="325" ht="16.5" customHeight="1"/>
-    <row r="326" ht="16.5" customHeight="1"/>
-    <row r="327" ht="16.5" customHeight="1"/>
-    <row r="328" ht="16.5" customHeight="1"/>
-    <row r="329" ht="16.5" customHeight="1"/>
-    <row r="330" ht="16.5" customHeight="1"/>
-    <row r="331" ht="16.5" customHeight="1"/>
-    <row r="332" ht="16.5" customHeight="1"/>
-    <row r="333" ht="16.5" customHeight="1"/>
-    <row r="334" ht="16.5" customHeight="1"/>
-    <row r="335" ht="16.5" customHeight="1"/>
-    <row r="336" ht="16.5" customHeight="1"/>
-    <row r="337" ht="16.5" customHeight="1"/>
-    <row r="338" ht="16.5" customHeight="1"/>
-    <row r="339" ht="16.5" customHeight="1"/>
-    <row r="340" ht="16.5" customHeight="1"/>
-    <row r="341" ht="16.5" customHeight="1"/>
-    <row r="342" ht="16.5" customHeight="1"/>
-    <row r="343" ht="16.5" customHeight="1"/>
-    <row r="344" ht="16.5" customHeight="1"/>
-    <row r="345" ht="16.5" customHeight="1"/>
-    <row r="346" ht="16.5" customHeight="1"/>
-    <row r="347" ht="16.5" customHeight="1"/>
-    <row r="348" ht="16.5" customHeight="1"/>
-    <row r="349" ht="16.5" customHeight="1"/>
-    <row r="350" ht="16.5" customHeight="1"/>
-    <row r="351" ht="16.5" customHeight="1"/>
-    <row r="352" ht="16.5" customHeight="1"/>
-    <row r="353" ht="16.5" customHeight="1"/>
-    <row r="354" ht="16.5" customHeight="1"/>
-    <row r="355" ht="16.5" customHeight="1"/>
-    <row r="356" ht="16.5" customHeight="1"/>
-    <row r="357" ht="16.5" customHeight="1"/>
-    <row r="358" ht="16.5" customHeight="1"/>
-    <row r="359" ht="16.5" customHeight="1"/>
-    <row r="360" ht="16.5" customHeight="1"/>
-    <row r="361" ht="16.5" customHeight="1"/>
-    <row r="362" ht="16.5" customHeight="1"/>
-    <row r="363" ht="16.5" customHeight="1"/>
-    <row r="364" ht="16.5" customHeight="1"/>
-    <row r="365" ht="16.5" customHeight="1"/>
-    <row r="366" ht="16.5" customHeight="1"/>
-    <row r="367" ht="16.5" customHeight="1"/>
-    <row r="368" ht="16.5" customHeight="1"/>
-    <row r="369" ht="16.5" customHeight="1"/>
-    <row r="370" ht="16.5" customHeight="1"/>
-    <row r="371" ht="16.5" customHeight="1"/>
-    <row r="372" ht="16.5" customHeight="1"/>
-    <row r="373" ht="16.5" customHeight="1"/>
-    <row r="374" ht="16.5" customHeight="1"/>
-    <row r="375" ht="16.5" customHeight="1"/>
-    <row r="376" ht="16.5" customHeight="1"/>
-    <row r="377" ht="16.5" customHeight="1"/>
-    <row r="378" ht="16.5" customHeight="1"/>
-    <row r="379" ht="16.5" customHeight="1"/>
-    <row r="380" ht="16.5" customHeight="1"/>
-    <row r="381" ht="16.5" customHeight="1"/>
-    <row r="382" ht="16.5" customHeight="1"/>
-    <row r="383" ht="16.5" customHeight="1"/>
-    <row r="384" ht="16.5" customHeight="1"/>
-    <row r="385" ht="16.5" customHeight="1"/>
-    <row r="386" ht="16.5" customHeight="1"/>
-    <row r="387" ht="16.5" customHeight="1"/>
-    <row r="388" ht="16.5" customHeight="1"/>
-    <row r="389" ht="16.5" customHeight="1"/>
-    <row r="390" ht="16.5" customHeight="1"/>
-    <row r="391" ht="16.5" customHeight="1"/>
-    <row r="392" ht="16.5" customHeight="1"/>
-    <row r="393" ht="16.5" customHeight="1"/>
-    <row r="394" ht="16.5" customHeight="1"/>
-    <row r="395" ht="16.5" customHeight="1"/>
-    <row r="396" ht="16.5" customHeight="1"/>
-    <row r="397" ht="16.5" customHeight="1"/>
-    <row r="398" ht="16.5" customHeight="1"/>
-    <row r="399" ht="16.5" customHeight="1"/>
-    <row r="400" ht="16.5" customHeight="1"/>
-    <row r="401" ht="16.5" customHeight="1"/>
-    <row r="402" ht="16.5" customHeight="1"/>
-    <row r="403" ht="16.5" customHeight="1"/>
-    <row r="404" ht="16.5" customHeight="1"/>
-    <row r="405" ht="16.5" customHeight="1"/>
-    <row r="406" ht="16.5" customHeight="1"/>
-    <row r="407" ht="16.5" customHeight="1"/>
-    <row r="408" ht="16.5" customHeight="1"/>
-    <row r="409" ht="16.5" customHeight="1"/>
-    <row r="410" ht="16.5" customHeight="1"/>
-    <row r="411" ht="16.5" customHeight="1"/>
-    <row r="412" ht="16.5" customHeight="1"/>
-    <row r="413" ht="16.5" customHeight="1"/>
-    <row r="414" ht="16.5" customHeight="1"/>
-    <row r="415" ht="16.5" customHeight="1"/>
-    <row r="416" ht="16.5" customHeight="1"/>
-    <row r="417" ht="16.5" customHeight="1"/>
-    <row r="418" ht="16.5" customHeight="1"/>
-    <row r="419" ht="16.5" customHeight="1"/>
-    <row r="420" ht="16.5" customHeight="1"/>
-    <row r="421" ht="16.5" customHeight="1"/>
-    <row r="422" ht="16.5" customHeight="1"/>
-    <row r="423" ht="16.5" customHeight="1"/>
-    <row r="424" ht="16.5" customHeight="1"/>
-    <row r="425" ht="16.5" customHeight="1"/>
-    <row r="426" ht="16.5" customHeight="1"/>
-    <row r="427" ht="16.5" customHeight="1"/>
-    <row r="428" ht="16.5" customHeight="1"/>
-    <row r="429" ht="16.5" customHeight="1"/>
-    <row r="430" ht="16.5" customHeight="1"/>
-    <row r="431" ht="16.5" customHeight="1"/>
-    <row r="432" ht="16.5" customHeight="1"/>
-    <row r="433" ht="16.5" customHeight="1"/>
-    <row r="434" ht="16.5" customHeight="1"/>
-    <row r="435" ht="16.5" customHeight="1"/>
-    <row r="436" ht="16.5" customHeight="1"/>
-    <row r="437" ht="16.5" customHeight="1"/>
-    <row r="438" ht="16.5" customHeight="1"/>
-    <row r="439" ht="16.5" customHeight="1"/>
-    <row r="440" ht="16.5" customHeight="1"/>
-    <row r="441" ht="16.5" customHeight="1"/>
-    <row r="442" ht="16.5" customHeight="1"/>
-    <row r="443" ht="16.5" customHeight="1"/>
-    <row r="444" ht="16.5" customHeight="1"/>
-    <row r="445" ht="16.5" customHeight="1"/>
-    <row r="446" ht="16.5" customHeight="1"/>
-    <row r="447" ht="16.5" customHeight="1"/>
-    <row r="448" ht="16.5" customHeight="1"/>
-    <row r="449" ht="16.5" customHeight="1"/>
-    <row r="450" ht="16.5" customHeight="1"/>
-    <row r="451" ht="16.5" customHeight="1"/>
-    <row r="452" ht="16.5" customHeight="1"/>
-    <row r="453" ht="16.5" customHeight="1"/>
-    <row r="454" ht="16.5" customHeight="1"/>
-    <row r="455" ht="16.5" customHeight="1"/>
-    <row r="456" ht="16.5" customHeight="1"/>
-    <row r="457" ht="16.5" customHeight="1"/>
-    <row r="458" ht="16.5" customHeight="1"/>
-    <row r="459" ht="16.5" customHeight="1"/>
-    <row r="460" ht="16.5" customHeight="1"/>
-    <row r="461" ht="16.5" customHeight="1"/>
-    <row r="462" ht="16.5" customHeight="1"/>
-    <row r="463" ht="16.5" customHeight="1"/>
-    <row r="464" ht="16.5" customHeight="1"/>
-    <row r="465" ht="16.5" customHeight="1"/>
-    <row r="466" ht="16.5" customHeight="1"/>
-    <row r="467" ht="16.5" customHeight="1"/>
-    <row r="468" ht="16.5" customHeight="1"/>
-    <row r="469" ht="16.5" customHeight="1"/>
-    <row r="470" ht="16.5" customHeight="1"/>
-    <row r="471" ht="16.5" customHeight="1"/>
-    <row r="472" ht="16.5" customHeight="1"/>
-    <row r="473" ht="16.5" customHeight="1"/>
-    <row r="474" ht="16.5" customHeight="1"/>
-    <row r="475" ht="16.5" customHeight="1"/>
-    <row r="476" ht="16.5" customHeight="1"/>
-    <row r="477" ht="16.5" customHeight="1"/>
-    <row r="478" ht="16.5" customHeight="1"/>
-    <row r="479" ht="16.5" customHeight="1"/>
-    <row r="480" ht="16.5" customHeight="1"/>
-    <row r="481" ht="16.5" customHeight="1"/>
-    <row r="482" ht="16.5" customHeight="1"/>
-    <row r="483" ht="16.5" customHeight="1"/>
-    <row r="484" ht="16.5" customHeight="1"/>
-    <row r="485" ht="16.5" customHeight="1"/>
-    <row r="486" ht="16.5" customHeight="1"/>
-    <row r="487" ht="16.5" customHeight="1"/>
-    <row r="488" ht="16.5" customHeight="1"/>
-    <row r="489" ht="16.5" customHeight="1"/>
-    <row r="490" ht="16.5" customHeight="1"/>
-    <row r="491" ht="16.5" customHeight="1"/>
-    <row r="492" ht="16.5" customHeight="1"/>
-    <row r="493" ht="16.5" customHeight="1"/>
-    <row r="494" ht="16.5" customHeight="1"/>
-    <row r="495" ht="16.5" customHeight="1"/>
-    <row r="496" ht="16.5" customHeight="1"/>
-    <row r="497" ht="16.5" customHeight="1"/>
-    <row r="498" ht="16.5" customHeight="1"/>
-    <row r="499" ht="16.5" customHeight="1"/>
-    <row r="500" ht="16.5" customHeight="1"/>
-    <row r="501" ht="16.5" customHeight="1"/>
-    <row r="502" ht="16.5" customHeight="1"/>
-    <row r="503" ht="16.5" customHeight="1"/>
-    <row r="504" ht="16.5" customHeight="1"/>
-    <row r="505" ht="16.5" customHeight="1"/>
-    <row r="506" ht="16.5" customHeight="1"/>
-    <row r="507" ht="16.5" customHeight="1"/>
-    <row r="508" ht="16.5" customHeight="1"/>
-    <row r="509" ht="16.5" customHeight="1"/>
-    <row r="510" ht="16.5" customHeight="1"/>
-    <row r="511" ht="16.5" customHeight="1"/>
-    <row r="512" ht="16.5" customHeight="1"/>
-    <row r="513" ht="16.5" customHeight="1"/>
-    <row r="514" ht="16.5" customHeight="1"/>
-    <row r="515" ht="16.5" customHeight="1"/>
-    <row r="516" ht="16.5" customHeight="1"/>
-    <row r="517" ht="16.5" customHeight="1"/>
-    <row r="518" ht="16.5" customHeight="1"/>
-    <row r="519" ht="16.5" customHeight="1"/>
-    <row r="520" ht="16.5" customHeight="1"/>
-    <row r="521" ht="16.5" customHeight="1"/>
-    <row r="522" ht="16.5" customHeight="1"/>
-    <row r="523" ht="16.5" customHeight="1"/>
-    <row r="524" ht="16.5" customHeight="1"/>
-    <row r="525" ht="16.5" customHeight="1"/>
-    <row r="526" ht="16.5" customHeight="1"/>
-    <row r="527" ht="16.5" customHeight="1"/>
-    <row r="528" ht="16.5" customHeight="1"/>
-    <row r="529" ht="16.5" customHeight="1"/>
-    <row r="530" ht="16.5" customHeight="1"/>
-    <row r="531" ht="16.5" customHeight="1"/>
-    <row r="532" ht="16.5" customHeight="1"/>
-    <row r="533" ht="16.5" customHeight="1"/>
-    <row r="534" ht="16.5" customHeight="1"/>
-    <row r="535" ht="16.5" customHeight="1"/>
-    <row r="536" ht="16.5" customHeight="1"/>
-    <row r="537" ht="16.5" customHeight="1"/>
-    <row r="538" ht="16.5" customHeight="1"/>
-    <row r="539" ht="16.5" customHeight="1"/>
-    <row r="540" ht="16.5" customHeight="1"/>
-    <row r="541" ht="16.5" customHeight="1"/>
-    <row r="542" ht="16.5" customHeight="1"/>
-    <row r="543" ht="16.5" customHeight="1"/>
-    <row r="544" ht="16.5" customHeight="1"/>
-    <row r="545" ht="16.5" customHeight="1"/>
-    <row r="546" ht="16.5" customHeight="1"/>
-    <row r="547" ht="16.5" customHeight="1"/>
-    <row r="548" ht="16.5" customHeight="1"/>
-    <row r="549" ht="16.5" customHeight="1"/>
-    <row r="550" ht="16.5" customHeight="1"/>
-    <row r="551" ht="16.5" customHeight="1"/>
-    <row r="552" ht="16.5" customHeight="1"/>
-    <row r="553" ht="16.5" customHeight="1"/>
-    <row r="554" ht="16.5" customHeight="1"/>
-    <row r="555" ht="16.5" customHeight="1"/>
-    <row r="556" ht="16.5" customHeight="1"/>
-    <row r="557" ht="16.5" customHeight="1"/>
-    <row r="558" ht="16.5" customHeight="1"/>
-    <row r="559" ht="16.5" customHeight="1"/>
-    <row r="560" ht="16.5" customHeight="1"/>
-    <row r="561" ht="16.5" customHeight="1"/>
-    <row r="562" ht="16.5" customHeight="1"/>
-    <row r="563" ht="16.5" customHeight="1"/>
-    <row r="564" ht="16.5" customHeight="1"/>
-    <row r="565" ht="16.5" customHeight="1"/>
-    <row r="566" ht="16.5" customHeight="1"/>
-    <row r="567" ht="16.5" customHeight="1"/>
-    <row r="568" ht="16.5" customHeight="1"/>
-    <row r="569" ht="16.5" customHeight="1"/>
-    <row r="570" ht="16.5" customHeight="1"/>
-    <row r="571" ht="16.5" customHeight="1"/>
-    <row r="572" ht="16.5" customHeight="1"/>
-    <row r="573" ht="16.5" customHeight="1"/>
-    <row r="574" ht="16.5" customHeight="1"/>
-    <row r="575" ht="16.5" customHeight="1"/>
-    <row r="576" ht="16.5" customHeight="1"/>
-    <row r="577" ht="16.5" customHeight="1"/>
-    <row r="578" ht="16.5" customHeight="1"/>
-    <row r="579" ht="16.5" customHeight="1"/>
-    <row r="580" ht="16.5" customHeight="1"/>
-    <row r="581" ht="16.5" customHeight="1"/>
-    <row r="582" ht="16.5" customHeight="1"/>
-    <row r="583" ht="16.5" customHeight="1"/>
-    <row r="584" ht="16.5" customHeight="1"/>
-    <row r="585" ht="16.5" customHeight="1"/>
-    <row r="586" ht="16.5" customHeight="1"/>
-    <row r="587" ht="16.5" customHeight="1"/>
-    <row r="588" ht="16.5" customHeight="1"/>
-    <row r="589" ht="16.5" customHeight="1"/>
-    <row r="590" ht="16.5" customHeight="1"/>
-    <row r="591" ht="16.5" customHeight="1"/>
-    <row r="592" ht="16.5" customHeight="1"/>
-    <row r="593" ht="16.5" customHeight="1"/>
-    <row r="594" ht="16.5" customHeight="1"/>
-    <row r="595" ht="16.5" customHeight="1"/>
-    <row r="596" ht="16.5" customHeight="1"/>
-    <row r="597" ht="16.5" customHeight="1"/>
-    <row r="598" ht="16.5" customHeight="1"/>
-    <row r="599" ht="16.5" customHeight="1"/>
-    <row r="600" ht="16.5" customHeight="1"/>
-    <row r="601" ht="16.5" customHeight="1"/>
-    <row r="602" ht="16.5" customHeight="1"/>
-    <row r="603" ht="16.5" customHeight="1"/>
-    <row r="604" ht="16.5" customHeight="1"/>
-    <row r="605" ht="16.5" customHeight="1"/>
-    <row r="606" ht="16.5" customHeight="1"/>
-    <row r="607" ht="16.5" customHeight="1"/>
-    <row r="608" ht="16.5" customHeight="1"/>
-    <row r="609" ht="16.5" customHeight="1"/>
-    <row r="610" ht="16.5" customHeight="1"/>
-    <row r="611" ht="16.5" customHeight="1"/>
-    <row r="612" ht="16.5" customHeight="1"/>
-    <row r="613" ht="16.5" customHeight="1"/>
-    <row r="614" ht="16.5" customHeight="1"/>
-    <row r="615" ht="16.5" customHeight="1"/>
-    <row r="616" ht="16.5" customHeight="1"/>
-    <row r="617" ht="16.5" customHeight="1"/>
-    <row r="618" ht="16.5" customHeight="1"/>
-    <row r="619" ht="16.5" customHeight="1"/>
-    <row r="620" ht="16.5" customHeight="1"/>
-    <row r="621" ht="16.5" customHeight="1"/>
-    <row r="622" ht="16.5" customHeight="1"/>
-    <row r="623" ht="16.5" customHeight="1"/>
-    <row r="624" ht="16.5" customHeight="1"/>
-    <row r="625" ht="16.5" customHeight="1"/>
-    <row r="626" ht="16.5" customHeight="1"/>
-    <row r="627" ht="16.5" customHeight="1"/>
-    <row r="628" ht="16.5" customHeight="1"/>
-    <row r="629" ht="16.5" customHeight="1"/>
-    <row r="630" ht="16.5" customHeight="1"/>
-    <row r="631" ht="16.5" customHeight="1"/>
-    <row r="632" ht="16.5" customHeight="1"/>
-    <row r="633" ht="16.5" customHeight="1"/>
-    <row r="634" ht="16.5" customHeight="1"/>
-    <row r="635" ht="16.5" customHeight="1"/>
-    <row r="636" ht="16.5" customHeight="1"/>
-    <row r="637" ht="16.5" customHeight="1"/>
-    <row r="638" ht="16.5" customHeight="1"/>
-    <row r="639" ht="16.5" customHeight="1"/>
-    <row r="640" ht="16.5" customHeight="1"/>
-    <row r="641" ht="16.5" customHeight="1"/>
-    <row r="642" ht="16.5" customHeight="1"/>
-    <row r="643" ht="16.5" customHeight="1"/>
-    <row r="644" ht="16.5" customHeight="1"/>
-    <row r="645" ht="16.5" customHeight="1"/>
-    <row r="646" ht="16.5" customHeight="1"/>
-    <row r="647" ht="16.5" customHeight="1"/>
-    <row r="648" ht="16.5" customHeight="1"/>
-    <row r="649" ht="16.5" customHeight="1"/>
-    <row r="650" ht="16.5" customHeight="1"/>
-    <row r="651" ht="16.5" customHeight="1"/>
-    <row r="652" ht="16.5" customHeight="1"/>
-    <row r="653" ht="16.5" customHeight="1"/>
-    <row r="654" ht="16.5" customHeight="1"/>
-    <row r="655" ht="16.5" customHeight="1"/>
-    <row r="656" ht="16.5" customHeight="1"/>
-    <row r="657" ht="16.5" customHeight="1"/>
-    <row r="658" ht="16.5" customHeight="1"/>
-    <row r="659" ht="16.5" customHeight="1"/>
-    <row r="660" ht="16.5" customHeight="1"/>
-    <row r="661" ht="16.5" customHeight="1"/>
-    <row r="662" ht="16.5" customHeight="1"/>
-    <row r="663" ht="16.5" customHeight="1"/>
-    <row r="664" ht="16.5" customHeight="1"/>
-    <row r="665" ht="16.5" customHeight="1"/>
-    <row r="666" ht="16.5" customHeight="1"/>
-    <row r="667" ht="16.5" customHeight="1"/>
-    <row r="668" ht="16.5" customHeight="1"/>
-    <row r="669" ht="16.5" customHeight="1"/>
-    <row r="670" ht="16.5" customHeight="1"/>
-    <row r="671" ht="16.5" customHeight="1"/>
-    <row r="672" ht="16.5" customHeight="1"/>
-    <row r="673" ht="16.5" customHeight="1"/>
-    <row r="674" ht="16.5" customHeight="1"/>
-    <row r="675" ht="16.5" customHeight="1"/>
-    <row r="676" ht="16.5" customHeight="1"/>
-    <row r="677" ht="16.5" customHeight="1"/>
-    <row r="678" ht="16.5" customHeight="1"/>
-    <row r="679" ht="16.5" customHeight="1"/>
-    <row r="680" ht="16.5" customHeight="1"/>
-    <row r="681" ht="16.5" customHeight="1"/>
-    <row r="682" ht="16.5" customHeight="1"/>
-    <row r="683" ht="16.5" customHeight="1"/>
-    <row r="684" ht="16.5" customHeight="1"/>
-    <row r="685" ht="16.5" customHeight="1"/>
-    <row r="686" ht="16.5" customHeight="1"/>
-    <row r="687" ht="16.5" customHeight="1"/>
-    <row r="688" ht="16.5" customHeight="1"/>
-    <row r="689" ht="16.5" customHeight="1"/>
-    <row r="690" ht="16.5" customHeight="1"/>
-    <row r="691" ht="16.5" customHeight="1"/>
-    <row r="692" ht="16.5" customHeight="1"/>
-    <row r="693" ht="16.5" customHeight="1"/>
-    <row r="694" ht="16.5" customHeight="1"/>
-    <row r="695" ht="16.5" customHeight="1"/>
-    <row r="696" ht="16.5" customHeight="1"/>
-    <row r="697" ht="16.5" customHeight="1"/>
-    <row r="698" ht="16.5" customHeight="1"/>
-    <row r="699" ht="16.5" customHeight="1"/>
-    <row r="700" ht="16.5" customHeight="1"/>
-    <row r="701" ht="16.5" customHeight="1"/>
-    <row r="702" ht="16.5" customHeight="1"/>
-    <row r="703" ht="16.5" customHeight="1"/>
-    <row r="704" ht="16.5" customHeight="1"/>
-    <row r="705" ht="16.5" customHeight="1"/>
-    <row r="706" ht="16.5" customHeight="1"/>
-    <row r="707" ht="16.5" customHeight="1"/>
-    <row r="708" ht="16.5" customHeight="1"/>
-    <row r="709" ht="16.5" customHeight="1"/>
-    <row r="710" ht="16.5" customHeight="1"/>
-    <row r="711" ht="16.5" customHeight="1"/>
-    <row r="712" ht="16.5" customHeight="1"/>
-    <row r="713" ht="16.5" customHeight="1"/>
-    <row r="714" ht="16.5" customHeight="1"/>
-    <row r="715" ht="16.5" customHeight="1"/>
-    <row r="716" ht="16.5" customHeight="1"/>
-    <row r="717" ht="16.5" customHeight="1"/>
-    <row r="718" ht="16.5" customHeight="1"/>
-    <row r="719" ht="16.5" customHeight="1"/>
-    <row r="720" ht="16.5" customHeight="1"/>
-    <row r="721" ht="16.5" customHeight="1"/>
-    <row r="722" ht="16.5" customHeight="1"/>
-    <row r="723" ht="16.5" customHeight="1"/>
-    <row r="724" ht="16.5" customHeight="1"/>
-    <row r="725" ht="16.5" customHeight="1"/>
-    <row r="726" ht="16.5" customHeight="1"/>
-    <row r="727" ht="16.5" customHeight="1"/>
-    <row r="728" ht="16.5" customHeight="1"/>
-    <row r="729" ht="16.5" customHeight="1"/>
-    <row r="730" ht="16.5" customHeight="1"/>
-    <row r="731" ht="16.5" customHeight="1"/>
-    <row r="732" ht="16.5" customHeight="1"/>
-    <row r="733" ht="16.5" customHeight="1"/>
-    <row r="734" ht="16.5" customHeight="1"/>
-    <row r="735" ht="16.5" customHeight="1"/>
-    <row r="736" ht="16.5" customHeight="1"/>
-    <row r="737" ht="16.5" customHeight="1"/>
-    <row r="738" ht="16.5" customHeight="1"/>
-    <row r="739" ht="16.5" customHeight="1"/>
-    <row r="740" ht="16.5" customHeight="1"/>
-    <row r="741" ht="16.5" customHeight="1"/>
-    <row r="742" ht="16.5" customHeight="1"/>
-    <row r="743" ht="16.5" customHeight="1"/>
-    <row r="744" ht="16.5" customHeight="1"/>
-    <row r="745" ht="16.5" customHeight="1"/>
-    <row r="746" ht="16.5" customHeight="1"/>
-    <row r="747" ht="16.5" customHeight="1"/>
-    <row r="748" ht="16.5" customHeight="1"/>
-    <row r="749" ht="16.5" customHeight="1"/>
-    <row r="750" ht="16.5" customHeight="1"/>
-    <row r="751" ht="16.5" customHeight="1"/>
-    <row r="752" ht="16.5" customHeight="1"/>
-    <row r="753" ht="16.5" customHeight="1"/>
-    <row r="754" ht="16.5" customHeight="1"/>
-    <row r="755" ht="16.5" customHeight="1"/>
-    <row r="756" ht="16.5" customHeight="1"/>
-    <row r="757" ht="16.5" customHeight="1"/>
-    <row r="758" ht="16.5" customHeight="1"/>
-    <row r="759" ht="16.5" customHeight="1"/>
-    <row r="760" ht="16.5" customHeight="1"/>
-    <row r="761" ht="16.5" customHeight="1"/>
-    <row r="762" ht="16.5" customHeight="1"/>
-    <row r="763" ht="16.5" customHeight="1"/>
-    <row r="764" ht="16.5" customHeight="1"/>
-    <row r="765" ht="16.5" customHeight="1"/>
-    <row r="766" ht="16.5" customHeight="1"/>
-    <row r="767" ht="16.5" customHeight="1"/>
-    <row r="768" ht="16.5" customHeight="1"/>
-    <row r="769" ht="16.5" customHeight="1"/>
-    <row r="770" ht="16.5" customHeight="1"/>
-    <row r="771" ht="16.5" customHeight="1"/>
-    <row r="772" ht="16.5" customHeight="1"/>
-    <row r="773" ht="16.5" customHeight="1"/>
-    <row r="774" ht="16.5" customHeight="1"/>
-    <row r="775" ht="16.5" customHeight="1"/>
-    <row r="776" ht="16.5" customHeight="1"/>
-    <row r="777" ht="16.5" customHeight="1"/>
-    <row r="778" ht="16.5" customHeight="1"/>
-    <row r="779" ht="16.5" customHeight="1"/>
-    <row r="780" ht="16.5" customHeight="1"/>
-    <row r="781" ht="16.5" customHeight="1"/>
-    <row r="782" ht="16.5" customHeight="1"/>
-    <row r="783" ht="16.5" customHeight="1"/>
-    <row r="784" ht="16.5" customHeight="1"/>
-    <row r="785" ht="16.5" customHeight="1"/>
-    <row r="786" ht="16.5" customHeight="1"/>
-    <row r="787" ht="16.5" customHeight="1"/>
-    <row r="788" ht="16.5" customHeight="1"/>
-    <row r="789" ht="16.5" customHeight="1"/>
-    <row r="790" ht="16.5" customHeight="1"/>
-    <row r="791" ht="16.5" customHeight="1"/>
-    <row r="792" ht="16.5" customHeight="1"/>
-    <row r="793" ht="16.5" customHeight="1"/>
-    <row r="794" ht="16.5" customHeight="1"/>
-    <row r="795" ht="16.5" customHeight="1"/>
-    <row r="796" ht="16.5" customHeight="1"/>
-    <row r="797" ht="16.5" customHeight="1"/>
-    <row r="798" ht="16.5" customHeight="1"/>
-    <row r="799" ht="16.5" customHeight="1"/>
-    <row r="800" ht="16.5" customHeight="1"/>
-    <row r="801" ht="16.5" customHeight="1"/>
-    <row r="802" ht="16.5" customHeight="1"/>
-    <row r="803" ht="16.5" customHeight="1"/>
-    <row r="804" ht="16.5" customHeight="1"/>
-    <row r="805" ht="16.5" customHeight="1"/>
-    <row r="806" ht="16.5" customHeight="1"/>
-    <row r="807" ht="16.5" customHeight="1"/>
-    <row r="808" ht="16.5" customHeight="1"/>
-    <row r="809" ht="16.5" customHeight="1"/>
-    <row r="810" ht="16.5" customHeight="1"/>
-    <row r="811" ht="16.5" customHeight="1"/>
-    <row r="812" ht="16.5" customHeight="1"/>
-    <row r="813" ht="16.5" customHeight="1"/>
-    <row r="814" ht="16.5" customHeight="1"/>
-    <row r="815" ht="16.5" customHeight="1"/>
-    <row r="816" ht="16.5" customHeight="1"/>
-    <row r="817" ht="16.5" customHeight="1"/>
-    <row r="818" ht="16.5" customHeight="1"/>
-    <row r="819" ht="16.5" customHeight="1"/>
-    <row r="820" ht="16.5" customHeight="1"/>
-    <row r="821" ht="16.5" customHeight="1"/>
-    <row r="822" ht="16.5" customHeight="1"/>
-    <row r="823" ht="16.5" customHeight="1"/>
-    <row r="824" ht="16.5" customHeight="1"/>
-    <row r="825" ht="16.5" customHeight="1"/>
-    <row r="826" ht="16.5" customHeight="1"/>
-    <row r="827" ht="16.5" customHeight="1"/>
-    <row r="828" ht="16.5" customHeight="1"/>
-    <row r="829" ht="16.5" customHeight="1"/>
-    <row r="830" ht="16.5" customHeight="1"/>
-    <row r="831" ht="16.5" customHeight="1"/>
-    <row r="832" ht="16.5" customHeight="1"/>
-    <row r="833" ht="16.5" customHeight="1"/>
-    <row r="834" ht="16.5" customHeight="1"/>
-    <row r="835" ht="16.5" customHeight="1"/>
-    <row r="836" ht="16.5" customHeight="1"/>
-    <row r="837" ht="16.5" customHeight="1"/>
-    <row r="838" ht="16.5" customHeight="1"/>
-    <row r="839" ht="16.5" customHeight="1"/>
-    <row r="840" ht="16.5" customHeight="1"/>
-    <row r="841" ht="16.5" customHeight="1"/>
-    <row r="842" ht="16.5" customHeight="1"/>
-    <row r="843" ht="16.5" customHeight="1"/>
-    <row r="844" ht="16.5" customHeight="1"/>
-    <row r="845" ht="16.5" customHeight="1"/>
-    <row r="846" ht="16.5" customHeight="1"/>
-    <row r="847" ht="16.5" customHeight="1"/>
-    <row r="848" ht="16.5" customHeight="1"/>
-    <row r="849" ht="16.5" customHeight="1"/>
-    <row r="850" ht="16.5" customHeight="1"/>
-    <row r="851" ht="16.5" customHeight="1"/>
-    <row r="852" ht="16.5" customHeight="1"/>
-    <row r="853" ht="16.5" customHeight="1"/>
-    <row r="854" ht="16.5" customHeight="1"/>
-    <row r="855" ht="16.5" customHeight="1"/>
-    <row r="856" ht="16.5" customHeight="1"/>
-    <row r="857" ht="16.5" customHeight="1"/>
-    <row r="858" ht="16.5" customHeight="1"/>
-    <row r="859" ht="16.5" customHeight="1"/>
-    <row r="860" ht="16.5" customHeight="1"/>
-    <row r="861" ht="16.5" customHeight="1"/>
-    <row r="862" ht="16.5" customHeight="1"/>
-    <row r="863" ht="16.5" customHeight="1"/>
-    <row r="864" ht="16.5" customHeight="1"/>
-    <row r="865" ht="16.5" customHeight="1"/>
-    <row r="866" ht="16.5" customHeight="1"/>
-    <row r="867" ht="16.5" customHeight="1"/>
-    <row r="868" ht="16.5" customHeight="1"/>
-    <row r="869" ht="16.5" customHeight="1"/>
-    <row r="870" ht="16.5" customHeight="1"/>
-    <row r="871" ht="16.5" customHeight="1"/>
-    <row r="872" ht="16.5" customHeight="1"/>
-    <row r="873" ht="16.5" customHeight="1"/>
-    <row r="874" ht="16.5" customHeight="1"/>
-    <row r="875" ht="16.5" customHeight="1"/>
-    <row r="876" ht="16.5" customHeight="1"/>
-    <row r="877" ht="16.5" customHeight="1"/>
-    <row r="878" ht="16.5" customHeight="1"/>
-    <row r="879" ht="16.5" customHeight="1"/>
-    <row r="880" ht="16.5" customHeight="1"/>
-    <row r="881" ht="16.5" customHeight="1"/>
-    <row r="882" ht="16.5" customHeight="1"/>
-    <row r="883" ht="16.5" customHeight="1"/>
-    <row r="884" ht="16.5" customHeight="1"/>
-    <row r="885" ht="16.5" customHeight="1"/>
-    <row r="886" ht="16.5" customHeight="1"/>
-    <row r="887" ht="16.5" customHeight="1"/>
-    <row r="888" ht="16.5" customHeight="1"/>
-    <row r="889" ht="16.5" customHeight="1"/>
-    <row r="890" ht="16.5" customHeight="1"/>
-    <row r="891" ht="16.5" customHeight="1"/>
-    <row r="892" ht="16.5" customHeight="1"/>
-    <row r="893" ht="16.5" customHeight="1"/>
-    <row r="894" ht="16.5" customHeight="1"/>
-    <row r="895" ht="16.5" customHeight="1"/>
-    <row r="896" ht="16.5" customHeight="1"/>
-    <row r="897" ht="16.5" customHeight="1"/>
-    <row r="898" ht="16.5" customHeight="1"/>
-    <row r="899" ht="16.5" customHeight="1"/>
-    <row r="900" ht="16.5" customHeight="1"/>
-    <row r="901" ht="16.5" customHeight="1"/>
-    <row r="902" ht="16.5" customHeight="1"/>
-    <row r="903" ht="16.5" customHeight="1"/>
-    <row r="904" ht="16.5" customHeight="1"/>
-    <row r="905" ht="16.5" customHeight="1"/>
-    <row r="906" ht="16.5" customHeight="1"/>
-    <row r="907" ht="16.5" customHeight="1"/>
-    <row r="908" ht="16.5" customHeight="1"/>
-    <row r="909" ht="16.5" customHeight="1"/>
-    <row r="910" ht="16.5" customHeight="1"/>
-    <row r="911" ht="16.5" customHeight="1"/>
-    <row r="912" ht="16.5" customHeight="1"/>
-    <row r="913" ht="16.5" customHeight="1"/>
-    <row r="914" ht="16.5" customHeight="1"/>
-    <row r="915" ht="16.5" customHeight="1"/>
-    <row r="916" ht="16.5" customHeight="1"/>
-    <row r="917" ht="16.5" customHeight="1"/>
-    <row r="918" ht="16.5" customHeight="1"/>
-    <row r="919" ht="16.5" customHeight="1"/>
-    <row r="920" ht="16.5" customHeight="1"/>
-    <row r="921" ht="16.5" customHeight="1"/>
-    <row r="922" ht="16.5" customHeight="1"/>
-    <row r="923" ht="16.5" customHeight="1"/>
-    <row r="924" ht="16.5" customHeight="1"/>
-    <row r="925" ht="16.5" customHeight="1"/>
-    <row r="926" ht="16.5" customHeight="1"/>
-    <row r="927" ht="16.5" customHeight="1"/>
-    <row r="928" ht="16.5" customHeight="1"/>
-    <row r="929" ht="16.5" customHeight="1"/>
-    <row r="930" ht="16.5" customHeight="1"/>
-    <row r="931" ht="16.5" customHeight="1"/>
-    <row r="932" ht="16.5" customHeight="1"/>
-    <row r="933" ht="16.5" customHeight="1"/>
-    <row r="934" ht="16.5" customHeight="1"/>
-    <row r="935" ht="16.5" customHeight="1"/>
-    <row r="936" ht="16.5" customHeight="1"/>
-    <row r="937" ht="16.5" customHeight="1"/>
-    <row r="938" ht="16.5" customHeight="1"/>
-    <row r="939" ht="16.5" customHeight="1"/>
-    <row r="940" ht="16.5" customHeight="1"/>
-    <row r="941" ht="16.5" customHeight="1"/>
-    <row r="942" ht="16.5" customHeight="1"/>
-    <row r="943" ht="16.5" customHeight="1"/>
-    <row r="944" ht="16.5" customHeight="1"/>
-    <row r="945" ht="16.5" customHeight="1"/>
-    <row r="946" ht="16.5" customHeight="1"/>
-    <row r="947" ht="16.5" customHeight="1"/>
-    <row r="948" ht="16.5" customHeight="1"/>
-    <row r="949" ht="16.5" customHeight="1"/>
-    <row r="950" ht="16.5" customHeight="1"/>
-    <row r="951" ht="16.5" customHeight="1"/>
-    <row r="952" ht="16.5" customHeight="1"/>
-    <row r="953" ht="16.5" customHeight="1"/>
-    <row r="954" ht="16.5" customHeight="1"/>
-    <row r="955" ht="16.5" customHeight="1"/>
-    <row r="956" ht="16.5" customHeight="1"/>
-    <row r="957" ht="16.5" customHeight="1"/>
-    <row r="958" ht="16.5" customHeight="1"/>
-    <row r="959" ht="16.5" customHeight="1"/>
-    <row r="960" ht="16.5" customHeight="1"/>
-    <row r="961" ht="16.5" customHeight="1"/>
-    <row r="962" ht="16.5" customHeight="1"/>
-    <row r="963" ht="16.5" customHeight="1"/>
-    <row r="964" ht="16.5" customHeight="1"/>
-    <row r="965" ht="16.5" customHeight="1"/>
-    <row r="966" ht="16.5" customHeight="1"/>
-    <row r="967" ht="16.5" customHeight="1"/>
-    <row r="968" ht="16.5" customHeight="1"/>
-    <row r="969" ht="16.5" customHeight="1"/>
-    <row r="970" ht="16.5" customHeight="1"/>
-    <row r="971" ht="16.5" customHeight="1"/>
-    <row r="972" ht="16.5" customHeight="1"/>
-    <row r="973" ht="16.5" customHeight="1"/>
-    <row r="974" ht="16.5" customHeight="1"/>
-    <row r="975" ht="16.5" customHeight="1"/>
-    <row r="976" ht="16.5" customHeight="1"/>
-    <row r="977" ht="16.5" customHeight="1"/>
-    <row r="978" ht="16.5" customHeight="1"/>
-    <row r="979" ht="16.5" customHeight="1"/>
-    <row r="980" ht="16.5" customHeight="1"/>
-    <row r="981" ht="16.5" customHeight="1"/>
-    <row r="982" ht="16.5" customHeight="1"/>
-    <row r="983" ht="16.5" customHeight="1"/>
-    <row r="984" ht="16.5" customHeight="1"/>
-    <row r="985" ht="16.5" customHeight="1"/>
-    <row r="986" ht="16.5" customHeight="1"/>
-    <row r="987" ht="16.5" customHeight="1"/>
-    <row r="988" ht="16.5" customHeight="1"/>
-    <row r="989" ht="16.5" customHeight="1"/>
-    <row r="990" ht="16.5" customHeight="1"/>
-    <row r="991" ht="16.5" customHeight="1"/>
-    <row r="992" ht="16.5" customHeight="1"/>
-    <row r="993" ht="16.5" customHeight="1"/>
-    <row r="994" ht="16.5" customHeight="1"/>
-    <row r="995" ht="16.5" customHeight="1"/>
-    <row r="996" ht="16.5" customHeight="1"/>
-    <row r="997" ht="16.5" customHeight="1"/>
-    <row r="998" ht="16.5" customHeight="1"/>
-    <row r="999" ht="16.5" customHeight="1"/>
-    <row r="1000" ht="16.5" customHeight="1"/>
-    <row r="1001" ht="16.5" customHeight="1"/>
-    <row r="1002" ht="16.5" customHeight="1"/>
-    <row r="1003" ht="16.5" customHeight="1"/>
-    <row r="1004" ht="16.5" customHeight="1"/>
-    <row r="1005" ht="16.5" customHeight="1"/>
-    <row r="1006" ht="16.5" customHeight="1"/>
+    <row r="99" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C99" s="50"/>
+      <c r="D99" s="50"/>
+      <c r="E99" s="50"/>
+      <c r="F99" s="50"/>
+      <c r="G99" s="50"/>
+      <c r="H99" s="50"/>
+      <c r="I99" s="50"/>
+      <c r="J99" s="50"/>
+      <c r="K99" s="52"/>
+    </row>
+    <row r="100" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C100" s="50"/>
+      <c r="D100" s="50"/>
+      <c r="E100" s="50"/>
+      <c r="F100" s="50"/>
+      <c r="G100" s="50"/>
+      <c r="H100" s="50"/>
+      <c r="I100" s="50"/>
+      <c r="J100" s="50"/>
+      <c r="K100" s="52"/>
+    </row>
+    <row r="101" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C101" s="50"/>
+      <c r="D101" s="50"/>
+      <c r="E101" s="50"/>
+      <c r="F101" s="50"/>
+      <c r="G101" s="50"/>
+      <c r="H101" s="50"/>
+      <c r="I101" s="50"/>
+      <c r="J101" s="50"/>
+      <c r="K101" s="52"/>
+    </row>
+    <row r="102" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C102" s="50"/>
+      <c r="D102" s="50"/>
+      <c r="E102" s="50"/>
+      <c r="F102" s="50"/>
+      <c r="G102" s="50"/>
+      <c r="H102" s="50"/>
+      <c r="I102" s="50"/>
+      <c r="J102" s="50"/>
+      <c r="K102" s="52"/>
+    </row>
+    <row r="103" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C103" s="50"/>
+      <c r="D103" s="50"/>
+      <c r="E103" s="50"/>
+      <c r="F103" s="50"/>
+      <c r="G103" s="50"/>
+      <c r="H103" s="50"/>
+      <c r="I103" s="50"/>
+      <c r="J103" s="50"/>
+      <c r="K103" s="52"/>
+    </row>
+    <row r="104" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C104" s="50"/>
+      <c r="D104" s="50"/>
+      <c r="E104" s="50"/>
+      <c r="F104" s="50"/>
+      <c r="G104" s="50"/>
+      <c r="H104" s="50"/>
+      <c r="I104" s="50"/>
+      <c r="J104" s="50"/>
+      <c r="K104" s="52"/>
+    </row>
+    <row r="105" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C105" s="50"/>
+      <c r="D105" s="50"/>
+      <c r="E105" s="50"/>
+      <c r="F105" s="50"/>
+      <c r="G105" s="50"/>
+      <c r="H105" s="50"/>
+      <c r="I105" s="50"/>
+      <c r="J105" s="50"/>
+      <c r="K105" s="52"/>
+    </row>
+    <row r="106" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C106" s="50"/>
+      <c r="D106" s="50"/>
+      <c r="E106" s="50"/>
+      <c r="F106" s="50"/>
+      <c r="G106" s="50"/>
+      <c r="H106" s="50"/>
+      <c r="I106" s="50"/>
+      <c r="J106" s="50"/>
+      <c r="K106" s="52"/>
+    </row>
+    <row r="107" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C107" s="50"/>
+      <c r="D107" s="50"/>
+      <c r="E107" s="50"/>
+      <c r="F107" s="50"/>
+      <c r="G107" s="50"/>
+      <c r="H107" s="50"/>
+      <c r="I107" s="50"/>
+      <c r="J107" s="50"/>
+      <c r="K107" s="52"/>
+    </row>
+    <row r="108" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C108" s="50"/>
+      <c r="D108" s="50"/>
+      <c r="E108" s="50"/>
+      <c r="F108" s="50"/>
+      <c r="G108" s="50"/>
+      <c r="H108" s="50"/>
+      <c r="I108" s="50"/>
+      <c r="J108" s="50"/>
+      <c r="K108" s="52"/>
+    </row>
+    <row r="109" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C109" s="50"/>
+      <c r="D109" s="50"/>
+      <c r="E109" s="50"/>
+      <c r="F109" s="50"/>
+      <c r="G109" s="50"/>
+      <c r="H109" s="50"/>
+      <c r="I109" s="50"/>
+      <c r="J109" s="50"/>
+      <c r="K109" s="52"/>
+    </row>
+    <row r="110" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C110" s="50"/>
+      <c r="D110" s="50"/>
+      <c r="E110" s="50"/>
+      <c r="F110" s="50"/>
+      <c r="G110" s="50"/>
+      <c r="H110" s="50"/>
+      <c r="I110" s="50"/>
+      <c r="J110" s="50"/>
+      <c r="K110" s="52"/>
+    </row>
+    <row r="111" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C111" s="50"/>
+      <c r="D111" s="50"/>
+      <c r="E111" s="50"/>
+      <c r="F111" s="50"/>
+      <c r="G111" s="50"/>
+      <c r="H111" s="50"/>
+      <c r="I111" s="50"/>
+      <c r="J111" s="50"/>
+      <c r="K111" s="52"/>
+    </row>
+    <row r="112" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C112" s="50"/>
+      <c r="D112" s="50"/>
+      <c r="E112" s="50"/>
+      <c r="F112" s="50"/>
+      <c r="G112" s="50"/>
+      <c r="H112" s="50"/>
+      <c r="I112" s="50"/>
+      <c r="J112" s="50"/>
+      <c r="K112" s="52"/>
+    </row>
+    <row r="113" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C113" s="48"/>
+      <c r="D113" s="48"/>
+      <c r="E113" s="48"/>
+      <c r="F113" s="48"/>
+      <c r="G113" s="48"/>
+      <c r="H113" s="48"/>
+      <c r="I113" s="48"/>
+      <c r="J113" s="48"/>
+      <c r="K113" s="48"/>
+    </row>
+    <row r="114" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C114" s="48"/>
+      <c r="D114" s="48"/>
+      <c r="E114" s="48"/>
+      <c r="F114" s="48"/>
+      <c r="G114" s="48"/>
+      <c r="H114" s="48"/>
+      <c r="I114" s="48"/>
+      <c r="J114" s="48"/>
+      <c r="K114" s="48"/>
+    </row>
+    <row r="115" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C115" s="48"/>
+      <c r="D115" s="48"/>
+      <c r="E115" s="48"/>
+      <c r="F115" s="48"/>
+      <c r="G115" s="48"/>
+      <c r="H115" s="48"/>
+      <c r="I115" s="48"/>
+      <c r="J115" s="48"/>
+      <c r="K115" s="48"/>
+    </row>
+    <row r="116" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C116" s="48"/>
+      <c r="D116" s="48"/>
+      <c r="E116" s="48"/>
+      <c r="F116" s="48"/>
+      <c r="G116" s="48"/>
+      <c r="H116" s="48"/>
+      <c r="I116" s="48"/>
+      <c r="J116" s="48"/>
+      <c r="K116" s="48"/>
+    </row>
+    <row r="117" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C117" s="48"/>
+      <c r="D117" s="48"/>
+      <c r="E117" s="48"/>
+      <c r="F117" s="48"/>
+      <c r="G117" s="48"/>
+      <c r="H117" s="48"/>
+      <c r="I117" s="48"/>
+      <c r="J117" s="48"/>
+      <c r="K117" s="48"/>
+    </row>
+    <row r="118" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C118" s="48"/>
+      <c r="D118" s="48"/>
+      <c r="E118" s="48"/>
+      <c r="F118" s="48"/>
+      <c r="G118" s="48"/>
+      <c r="H118" s="48"/>
+      <c r="I118" s="48"/>
+      <c r="J118" s="48"/>
+      <c r="K118" s="48"/>
+    </row>
+    <row r="119" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C119" s="48"/>
+      <c r="D119" s="48"/>
+      <c r="E119" s="48"/>
+      <c r="F119" s="48"/>
+      <c r="G119" s="48"/>
+      <c r="H119" s="48"/>
+      <c r="I119" s="48"/>
+      <c r="J119" s="48"/>
+      <c r="K119" s="48"/>
+    </row>
+    <row r="120" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C120" s="48"/>
+      <c r="D120" s="48"/>
+      <c r="E120" s="48"/>
+      <c r="F120" s="48"/>
+      <c r="G120" s="48"/>
+      <c r="H120" s="48"/>
+      <c r="I120" s="48"/>
+      <c r="J120" s="48"/>
+      <c r="K120" s="48"/>
+    </row>
+    <row r="121" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C121" s="48"/>
+      <c r="D121" s="48"/>
+      <c r="E121" s="48"/>
+      <c r="F121" s="48"/>
+      <c r="G121" s="48"/>
+      <c r="H121" s="48"/>
+      <c r="I121" s="48"/>
+      <c r="J121" s="48"/>
+      <c r="K121" s="48"/>
+    </row>
+    <row r="122" ht="16.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C122" s="48"/>
+      <c r="D122" s="48"/>
+      <c r="E122" s="48"/>
+      <c r="F122" s="48"/>
+      <c r="G122" s="48"/>
+      <c r="H122" s="48"/>
+      <c r="I122" s="48"/>
+      <c r="J122" s="48"/>
+      <c r="K122" s="48"/>
+    </row>
+    <row r="123" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1001" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1002" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1003" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1004" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1005" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1006" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1007" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1008" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1009" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1010" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1011" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1012" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1013" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1014" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1015" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1016" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1017" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1018" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1019" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1020" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="54">
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B4:K4"/>
@@ -4219,2606 +4591,2633 @@
     <mergeCell ref="G23:H23"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="G24:H24"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="D50:J50"/>
-    <mergeCell ref="D51:J51"/>
-    <mergeCell ref="D57:G57"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="G26:H26"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="G27:H27"/>
+    <mergeCell ref="C28:F28"/>
     <mergeCell ref="G28:H28"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="C42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="C43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="D64:J64"/>
+    <mergeCell ref="D65:J65"/>
+    <mergeCell ref="D71:G71"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins bottom="0.25439127801332534" footer="0.0" header="0.0" left="0.49251968503937005" right="0.25" top="0.5454767701255973"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.49251968503937005" right="0.25" top="0.5454767701255973" bottom="0.25439127801332534" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:Z187"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.43"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="23.57"/>
-    <col customWidth="1" min="2" max="2" width="35.0"/>
-    <col customWidth="1" min="3" max="3" width="76.0"/>
+    <col min="1" max="1" width="23.57" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="76" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="61.5" customHeight="1">
-      <c r="A1" s="58" t="s">
+    <row r="1" ht="61.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="60" t="s">
+      <c r="C1" s="58" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" ht="61.5" customHeight="1">
-      <c r="A2" s="61" t="s">
+    <row r="2" ht="61.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="63"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="64" t="s">
+      <c r="B2" s="60"/>
+      <c r="C2" s="61"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="66" t="s">
+      <c r="C3" s="64" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="67" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="69" t="s">
+      <c r="C4" s="67" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="67" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="69" t="s">
+      <c r="C5" s="67" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="70" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="71" t="s">
+      <c r="B6" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="70" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="67" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="68" t="s">
+      <c r="B7" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="67" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="73" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="71" t="s">
+      <c r="B8" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="72" t="s">
+      <c r="C8" s="70" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="67" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="68" t="s">
+      <c r="B9" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="67" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="67" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="68" t="s">
+      <c r="B10" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="69" t="s">
+      <c r="C10" s="67" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="67" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="65" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="68" t="s">
+      <c r="B11" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="69" t="s">
+      <c r="C11" s="67" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="73" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="71" t="s">
+      <c r="B12" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="72" t="s">
+      <c r="C12" s="70" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="67" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="67" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="67" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="68" t="s">
+      <c r="B14" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="69" t="s">
+      <c r="C14" s="67" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="67" t="s">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="68" t="s">
+      <c r="B15" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="69" t="s">
+      <c r="C15" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="74"/>
-      <c r="I15" s="74"/>
-      <c r="J15" s="74"/>
-      <c r="K15" s="74"/>
-      <c r="L15" s="74"/>
-      <c r="M15" s="74"/>
-      <c r="N15" s="74"/>
-      <c r="O15" s="74"/>
-      <c r="P15" s="74"/>
-      <c r="Q15" s="74"/>
-      <c r="R15" s="74"/>
-      <c r="S15" s="74"/>
-      <c r="T15" s="74"/>
-      <c r="U15" s="74"/>
-      <c r="V15" s="74"/>
-      <c r="W15" s="74"/>
-      <c r="X15" s="74"/>
-      <c r="Y15" s="74"/>
-      <c r="Z15" s="74"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="73" t="s">
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="72"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="72"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="72"/>
+      <c r="O15" s="72"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="72"/>
+      <c r="T15" s="72"/>
+      <c r="U15" s="72"/>
+      <c r="V15" s="72"/>
+      <c r="W15" s="72"/>
+      <c r="X15" s="72"/>
+      <c r="Y15" s="72"/>
+      <c r="Z15" s="72"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="71" t="s">
+      <c r="B16" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="72" t="s">
+      <c r="C16" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
-      <c r="I16" s="74"/>
-      <c r="J16" s="74"/>
-      <c r="K16" s="74"/>
-      <c r="L16" s="74"/>
-      <c r="M16" s="74"/>
-      <c r="N16" s="74"/>
-      <c r="O16" s="74"/>
-      <c r="P16" s="74"/>
-      <c r="Q16" s="74"/>
-      <c r="R16" s="74"/>
-      <c r="S16" s="74"/>
-      <c r="T16" s="74"/>
-      <c r="U16" s="74"/>
-      <c r="V16" s="74"/>
-      <c r="W16" s="74"/>
-      <c r="X16" s="74"/>
-      <c r="Y16" s="74"/>
-      <c r="Z16" s="74"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="67" t="s">
+      <c r="D16" s="72"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="72"/>
+      <c r="M16" s="72"/>
+      <c r="N16" s="72"/>
+      <c r="O16" s="72"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72"/>
+      <c r="T16" s="72"/>
+      <c r="U16" s="72"/>
+      <c r="V16" s="72"/>
+      <c r="W16" s="72"/>
+      <c r="X16" s="72"/>
+      <c r="Y16" s="72"/>
+      <c r="Z16" s="72"/>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A17" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="69" t="s">
+      <c r="C17" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="74"/>
-      <c r="I17" s="74"/>
-      <c r="J17" s="74"/>
-      <c r="K17" s="74"/>
-      <c r="L17" s="74"/>
-      <c r="M17" s="74"/>
-      <c r="N17" s="74"/>
-      <c r="O17" s="74"/>
-      <c r="P17" s="74"/>
-      <c r="Q17" s="74"/>
-      <c r="R17" s="74"/>
-      <c r="S17" s="74"/>
-      <c r="T17" s="74"/>
-      <c r="U17" s="74"/>
-      <c r="V17" s="74"/>
-      <c r="W17" s="74"/>
-      <c r="X17" s="74"/>
-      <c r="Y17" s="74"/>
-      <c r="Z17" s="74"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="67" t="s">
+      <c r="D17" s="72"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="72"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="72"/>
+      <c r="I17" s="72"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="72"/>
+      <c r="M17" s="72"/>
+      <c r="N17" s="72"/>
+      <c r="O17" s="72"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="72"/>
+      <c r="T17" s="72"/>
+      <c r="U17" s="72"/>
+      <c r="V17" s="72"/>
+      <c r="W17" s="72"/>
+      <c r="X17" s="72"/>
+      <c r="Y17" s="72"/>
+      <c r="Z17" s="72"/>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A18" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="68" t="s">
+      <c r="B18" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="69" t="s">
+      <c r="C18" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="74"/>
-      <c r="H18" s="74"/>
-      <c r="I18" s="74"/>
-      <c r="J18" s="74"/>
-      <c r="K18" s="74"/>
-      <c r="L18" s="74"/>
-      <c r="M18" s="74"/>
-      <c r="N18" s="74"/>
-      <c r="O18" s="74"/>
-      <c r="P18" s="74"/>
-      <c r="Q18" s="74"/>
-      <c r="R18" s="74"/>
-      <c r="S18" s="74"/>
-      <c r="T18" s="74"/>
-      <c r="U18" s="74"/>
-      <c r="V18" s="74"/>
-      <c r="W18" s="74"/>
-      <c r="X18" s="74"/>
-      <c r="Y18" s="74"/>
-      <c r="Z18" s="74"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="67" t="s">
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="72"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="72"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="72"/>
+      <c r="M18" s="72"/>
+      <c r="N18" s="72"/>
+      <c r="O18" s="72"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="72"/>
+      <c r="T18" s="72"/>
+      <c r="U18" s="72"/>
+      <c r="V18" s="72"/>
+      <c r="W18" s="72"/>
+      <c r="X18" s="72"/>
+      <c r="Y18" s="72"/>
+      <c r="Z18" s="72"/>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A19" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="68" t="s">
+      <c r="B19" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="69" t="s">
+      <c r="C19" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="74"/>
-      <c r="J19" s="74"/>
-      <c r="K19" s="74"/>
-      <c r="L19" s="74"/>
-      <c r="M19" s="74"/>
-      <c r="N19" s="74"/>
-      <c r="O19" s="74"/>
-      <c r="P19" s="74"/>
-      <c r="Q19" s="74"/>
-      <c r="R19" s="74"/>
-      <c r="S19" s="74"/>
-      <c r="T19" s="74"/>
-      <c r="U19" s="74"/>
-      <c r="V19" s="74"/>
-      <c r="W19" s="74"/>
-      <c r="X19" s="74"/>
-      <c r="Y19" s="74"/>
-      <c r="Z19" s="74"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="73" t="s">
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="72"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="72"/>
+      <c r="M19" s="72"/>
+      <c r="N19" s="72"/>
+      <c r="O19" s="72"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="72"/>
+      <c r="T19" s="72"/>
+      <c r="U19" s="72"/>
+      <c r="V19" s="72"/>
+      <c r="W19" s="72"/>
+      <c r="X19" s="72"/>
+      <c r="Y19" s="72"/>
+      <c r="Z19" s="72"/>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A20" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="B20" s="71" t="s">
+      <c r="B20" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="72" t="s">
+      <c r="C20" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="74"/>
-      <c r="J20" s="74"/>
-      <c r="K20" s="74"/>
-      <c r="L20" s="74"/>
-      <c r="M20" s="74"/>
-      <c r="N20" s="74"/>
-      <c r="O20" s="74"/>
-      <c r="P20" s="74"/>
-      <c r="Q20" s="74"/>
-      <c r="R20" s="74"/>
-      <c r="S20" s="74"/>
-      <c r="T20" s="74"/>
-      <c r="U20" s="74"/>
-      <c r="V20" s="74"/>
-      <c r="W20" s="74"/>
-      <c r="X20" s="74"/>
-      <c r="Y20" s="74"/>
-      <c r="Z20" s="74"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="67" t="s">
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="72"/>
+      <c r="H20" s="72"/>
+      <c r="I20" s="72"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="72"/>
+      <c r="M20" s="72"/>
+      <c r="N20" s="72"/>
+      <c r="O20" s="72"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="72"/>
+      <c r="T20" s="72"/>
+      <c r="U20" s="72"/>
+      <c r="V20" s="72"/>
+      <c r="W20" s="72"/>
+      <c r="X20" s="72"/>
+      <c r="Y20" s="72"/>
+      <c r="Z20" s="72"/>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A21" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="68" t="s">
+      <c r="B21" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="69" t="s">
+      <c r="C21" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="74"/>
-      <c r="E21" s="74"/>
-      <c r="F21" s="74"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="74"/>
-      <c r="J21" s="74"/>
-      <c r="K21" s="74"/>
-      <c r="L21" s="74"/>
-      <c r="M21" s="74"/>
-      <c r="N21" s="74"/>
-      <c r="O21" s="74"/>
-      <c r="P21" s="74"/>
-      <c r="Q21" s="74"/>
-      <c r="R21" s="74"/>
-      <c r="S21" s="74"/>
-      <c r="T21" s="74"/>
-      <c r="U21" s="74"/>
-      <c r="V21" s="74"/>
-      <c r="W21" s="74"/>
-      <c r="X21" s="74"/>
-      <c r="Y21" s="74"/>
-      <c r="Z21" s="74"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="67" t="s">
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="72"/>
+      <c r="M21" s="72"/>
+      <c r="N21" s="72"/>
+      <c r="O21" s="72"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="72"/>
+      <c r="T21" s="72"/>
+      <c r="U21" s="72"/>
+      <c r="V21" s="72"/>
+      <c r="W21" s="72"/>
+      <c r="X21" s="72"/>
+      <c r="Y21" s="72"/>
+      <c r="Z21" s="72"/>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A22" s="65" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="68" t="s">
+      <c r="B22" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="69" t="s">
+      <c r="C22" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="74"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="74"/>
-      <c r="J22" s="74"/>
-      <c r="K22" s="74"/>
-      <c r="L22" s="74"/>
-      <c r="M22" s="74"/>
-      <c r="N22" s="74"/>
-      <c r="O22" s="74"/>
-      <c r="P22" s="74"/>
-      <c r="Q22" s="74"/>
-      <c r="R22" s="74"/>
-      <c r="S22" s="74"/>
-      <c r="T22" s="74"/>
-      <c r="U22" s="74"/>
-      <c r="V22" s="74"/>
-      <c r="W22" s="74"/>
-      <c r="X22" s="74"/>
-      <c r="Y22" s="74"/>
-      <c r="Z22" s="74"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="73" t="s">
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="72"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="72"/>
+      <c r="T22" s="72"/>
+      <c r="U22" s="72"/>
+      <c r="V22" s="72"/>
+      <c r="W22" s="72"/>
+      <c r="X22" s="72"/>
+      <c r="Y22" s="72"/>
+      <c r="Z22" s="72"/>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A23" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="71" t="s">
+      <c r="B23" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="72" t="s">
+      <c r="C23" s="70" t="s">
         <v>71</v>
       </c>
-      <c r="D23" s="74"/>
-      <c r="E23" s="74"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="74"/>
-      <c r="I23" s="74"/>
-      <c r="J23" s="74"/>
-      <c r="K23" s="74"/>
-      <c r="L23" s="74"/>
-      <c r="M23" s="74"/>
-      <c r="N23" s="74"/>
-      <c r="O23" s="74"/>
-      <c r="P23" s="74"/>
-      <c r="Q23" s="74"/>
-      <c r="R23" s="74"/>
-      <c r="S23" s="74"/>
-      <c r="T23" s="74"/>
-      <c r="U23" s="74"/>
-      <c r="V23" s="74"/>
-      <c r="W23" s="74"/>
-      <c r="X23" s="74"/>
-      <c r="Y23" s="74"/>
-      <c r="Z23" s="74"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="67" t="s">
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="72"/>
+      <c r="M23" s="72"/>
+      <c r="N23" s="72"/>
+      <c r="O23" s="72"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="72"/>
+      <c r="T23" s="72"/>
+      <c r="U23" s="72"/>
+      <c r="V23" s="72"/>
+      <c r="W23" s="72"/>
+      <c r="X23" s="72"/>
+      <c r="Y23" s="72"/>
+      <c r="Z23" s="72"/>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A24" s="65" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="68" t="s">
+      <c r="B24" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="69" t="s">
+      <c r="C24" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="74"/>
-      <c r="I24" s="74"/>
-      <c r="J24" s="74"/>
-      <c r="K24" s="74"/>
-      <c r="L24" s="74"/>
-      <c r="M24" s="74"/>
-      <c r="N24" s="74"/>
-      <c r="O24" s="74"/>
-      <c r="P24" s="74"/>
-      <c r="Q24" s="74"/>
-      <c r="R24" s="74"/>
-      <c r="S24" s="74"/>
-      <c r="T24" s="74"/>
-      <c r="U24" s="74"/>
-      <c r="V24" s="74"/>
-      <c r="W24" s="74"/>
-      <c r="X24" s="74"/>
-      <c r="Y24" s="74"/>
-      <c r="Z24" s="74"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="67" t="s">
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="72"/>
+      <c r="O24" s="72"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="72"/>
+      <c r="T24" s="72"/>
+      <c r="U24" s="72"/>
+      <c r="V24" s="72"/>
+      <c r="W24" s="72"/>
+      <c r="X24" s="72"/>
+      <c r="Y24" s="72"/>
+      <c r="Z24" s="72"/>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A25" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="68" t="s">
+      <c r="B25" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="69" t="s">
+      <c r="C25" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="D25" s="74"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74"/>
-      <c r="I25" s="74"/>
-      <c r="J25" s="74"/>
-      <c r="K25" s="74"/>
-      <c r="L25" s="74"/>
-      <c r="M25" s="74"/>
-      <c r="N25" s="74"/>
-      <c r="O25" s="74"/>
-      <c r="P25" s="74"/>
-      <c r="Q25" s="74"/>
-      <c r="R25" s="74"/>
-      <c r="S25" s="74"/>
-      <c r="T25" s="74"/>
-      <c r="U25" s="74"/>
-      <c r="V25" s="74"/>
-      <c r="W25" s="74"/>
-      <c r="X25" s="74"/>
-      <c r="Y25" s="74"/>
-      <c r="Z25" s="74"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="73" t="s">
+      <c r="D25" s="72"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="72"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="72"/>
+      <c r="I25" s="72"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="72"/>
+      <c r="M25" s="72"/>
+      <c r="N25" s="72"/>
+      <c r="O25" s="72"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="72"/>
+      <c r="T25" s="72"/>
+      <c r="U25" s="72"/>
+      <c r="V25" s="72"/>
+      <c r="W25" s="72"/>
+      <c r="X25" s="72"/>
+      <c r="Y25" s="72"/>
+      <c r="Z25" s="72"/>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A26" s="71" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="71" t="s">
+      <c r="B26" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="72" t="s">
+      <c r="C26" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-      <c r="I26" s="74"/>
-      <c r="J26" s="74"/>
-      <c r="K26" s="74"/>
-      <c r="L26" s="74"/>
-      <c r="M26" s="74"/>
-      <c r="N26" s="74"/>
-      <c r="O26" s="74"/>
-      <c r="P26" s="74"/>
-      <c r="Q26" s="74"/>
-      <c r="R26" s="74"/>
-      <c r="S26" s="74"/>
-      <c r="T26" s="74"/>
-      <c r="U26" s="74"/>
-      <c r="V26" s="74"/>
-      <c r="W26" s="74"/>
-      <c r="X26" s="74"/>
-      <c r="Y26" s="74"/>
-      <c r="Z26" s="74"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="67" t="s">
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="72"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="72"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="72"/>
+      <c r="N26" s="72"/>
+      <c r="O26" s="72"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="72"/>
+      <c r="T26" s="72"/>
+      <c r="U26" s="72"/>
+      <c r="V26" s="72"/>
+      <c r="W26" s="72"/>
+      <c r="X26" s="72"/>
+      <c r="Y26" s="72"/>
+      <c r="Z26" s="72"/>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A27" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="B27" s="68" t="s">
+      <c r="B27" s="66" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="69" t="s">
+      <c r="C27" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="D27" s="74"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="74"/>
-      <c r="H27" s="74"/>
-      <c r="I27" s="74"/>
-      <c r="J27" s="74"/>
-      <c r="K27" s="74"/>
-      <c r="L27" s="74"/>
-      <c r="M27" s="74"/>
-      <c r="N27" s="74"/>
-      <c r="O27" s="74"/>
-      <c r="P27" s="74"/>
-      <c r="Q27" s="74"/>
-      <c r="R27" s="74"/>
-      <c r="S27" s="74"/>
-      <c r="T27" s="74"/>
-      <c r="U27" s="74"/>
-      <c r="V27" s="74"/>
-      <c r="W27" s="74"/>
-      <c r="X27" s="74"/>
-      <c r="Y27" s="74"/>
-      <c r="Z27" s="74"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="67" t="s">
+      <c r="D27" s="72"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="72"/>
+      <c r="G27" s="72"/>
+      <c r="H27" s="72"/>
+      <c r="I27" s="72"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="72"/>
+      <c r="M27" s="72"/>
+      <c r="N27" s="72"/>
+      <c r="O27" s="72"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="72"/>
+      <c r="T27" s="72"/>
+      <c r="U27" s="72"/>
+      <c r="V27" s="72"/>
+      <c r="W27" s="72"/>
+      <c r="X27" s="72"/>
+      <c r="Y27" s="72"/>
+      <c r="Z27" s="72"/>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A28" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="B28" s="68" t="s">
+      <c r="B28" s="66" t="s">
         <v>74</v>
       </c>
-      <c r="C28" s="69" t="s">
+      <c r="C28" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="D28" s="74"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
-      <c r="I28" s="74"/>
-      <c r="J28" s="74"/>
-      <c r="K28" s="74"/>
-      <c r="L28" s="74"/>
-      <c r="M28" s="74"/>
-      <c r="N28" s="74"/>
-      <c r="O28" s="74"/>
-      <c r="P28" s="74"/>
-      <c r="Q28" s="74"/>
-      <c r="R28" s="74"/>
-      <c r="S28" s="74"/>
-      <c r="T28" s="74"/>
-      <c r="U28" s="74"/>
-      <c r="V28" s="74"/>
-      <c r="W28" s="74"/>
-      <c r="X28" s="74"/>
-      <c r="Y28" s="74"/>
-      <c r="Z28" s="74"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="73" t="s">
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
+      <c r="I28" s="72"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="72"/>
+      <c r="M28" s="72"/>
+      <c r="N28" s="72"/>
+      <c r="O28" s="72"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="72"/>
+      <c r="T28" s="72"/>
+      <c r="U28" s="72"/>
+      <c r="V28" s="72"/>
+      <c r="W28" s="72"/>
+      <c r="X28" s="72"/>
+      <c r="Y28" s="72"/>
+      <c r="Z28" s="72"/>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A29" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="B29" s="71" t="s">
+      <c r="B29" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="C29" s="72" t="s">
+      <c r="C29" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="D29" s="74"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74"/>
-      <c r="I29" s="74"/>
-      <c r="J29" s="74"/>
-      <c r="K29" s="74"/>
-      <c r="L29" s="74"/>
-      <c r="M29" s="74"/>
-      <c r="N29" s="74"/>
-      <c r="O29" s="74"/>
-      <c r="P29" s="74"/>
-      <c r="Q29" s="74"/>
-      <c r="R29" s="74"/>
-      <c r="S29" s="74"/>
-      <c r="T29" s="74"/>
-      <c r="U29" s="74"/>
-      <c r="V29" s="74"/>
-      <c r="W29" s="74"/>
-      <c r="X29" s="74"/>
-      <c r="Y29" s="74"/>
-      <c r="Z29" s="74"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="67" t="s">
+      <c r="D29" s="72"/>
+      <c r="E29" s="72"/>
+      <c r="F29" s="72"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="72"/>
+      <c r="I29" s="72"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="72"/>
+      <c r="M29" s="72"/>
+      <c r="N29" s="72"/>
+      <c r="O29" s="72"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="72"/>
+      <c r="T29" s="72"/>
+      <c r="U29" s="72"/>
+      <c r="V29" s="72"/>
+      <c r="W29" s="72"/>
+      <c r="X29" s="72"/>
+      <c r="Y29" s="72"/>
+      <c r="Z29" s="72"/>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A30" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="68" t="s">
+      <c r="B30" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="C30" s="69" t="s">
+      <c r="C30" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="74"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
-      <c r="I30" s="74"/>
-      <c r="J30" s="74"/>
-      <c r="K30" s="74"/>
-      <c r="L30" s="74"/>
-      <c r="M30" s="74"/>
-      <c r="N30" s="74"/>
-      <c r="O30" s="74"/>
-      <c r="P30" s="74"/>
-      <c r="Q30" s="74"/>
-      <c r="R30" s="74"/>
-      <c r="S30" s="74"/>
-      <c r="T30" s="74"/>
-      <c r="U30" s="74"/>
-      <c r="V30" s="74"/>
-      <c r="W30" s="74"/>
-      <c r="X30" s="74"/>
-      <c r="Y30" s="74"/>
-      <c r="Z30" s="74"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="67" t="s">
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="72"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="72"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="72"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="72"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="72"/>
+      <c r="T30" s="72"/>
+      <c r="U30" s="72"/>
+      <c r="V30" s="72"/>
+      <c r="W30" s="72"/>
+      <c r="X30" s="72"/>
+      <c r="Y30" s="72"/>
+      <c r="Z30" s="72"/>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A31" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="B31" s="68" t="s">
+      <c r="B31" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="69" t="s">
+      <c r="C31" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="74"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="74"/>
-      <c r="J31" s="74"/>
-      <c r="K31" s="74"/>
-      <c r="L31" s="74"/>
-      <c r="M31" s="74"/>
-      <c r="N31" s="74"/>
-      <c r="O31" s="74"/>
-      <c r="P31" s="74"/>
-      <c r="Q31" s="74"/>
-      <c r="R31" s="74"/>
-      <c r="S31" s="74"/>
-      <c r="T31" s="74"/>
-      <c r="U31" s="74"/>
-      <c r="V31" s="74"/>
-      <c r="W31" s="74"/>
-      <c r="X31" s="74"/>
-      <c r="Y31" s="74"/>
-      <c r="Z31" s="74"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="73" t="s">
+      <c r="D31" s="72"/>
+      <c r="E31" s="72"/>
+      <c r="F31" s="72"/>
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="72"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="72"/>
+      <c r="O31" s="72"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="72"/>
+      <c r="T31" s="72"/>
+      <c r="U31" s="72"/>
+      <c r="V31" s="72"/>
+      <c r="W31" s="72"/>
+      <c r="X31" s="72"/>
+      <c r="Y31" s="72"/>
+      <c r="Z31" s="72"/>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A32" s="71" t="s">
         <v>81</v>
       </c>
-      <c r="B32" s="71" t="s">
+      <c r="B32" s="69" t="s">
         <v>82</v>
       </c>
-      <c r="C32" s="72" t="s">
+      <c r="C32" s="70" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="74"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="74"/>
-      <c r="H32" s="74"/>
-      <c r="I32" s="74"/>
-      <c r="J32" s="74"/>
-      <c r="K32" s="74"/>
-      <c r="L32" s="74"/>
-      <c r="M32" s="74"/>
-      <c r="N32" s="74"/>
-      <c r="O32" s="74"/>
-      <c r="P32" s="74"/>
-      <c r="Q32" s="74"/>
-      <c r="R32" s="74"/>
-      <c r="S32" s="74"/>
-      <c r="T32" s="74"/>
-      <c r="U32" s="74"/>
-      <c r="V32" s="74"/>
-      <c r="W32" s="74"/>
-      <c r="X32" s="74"/>
-      <c r="Y32" s="74"/>
-      <c r="Z32" s="74"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="67" t="s">
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="72"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="72"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="72"/>
+      <c r="M32" s="72"/>
+      <c r="N32" s="72"/>
+      <c r="O32" s="72"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="72"/>
+      <c r="T32" s="72"/>
+      <c r="U32" s="72"/>
+      <c r="V32" s="72"/>
+      <c r="W32" s="72"/>
+      <c r="X32" s="72"/>
+      <c r="Y32" s="72"/>
+      <c r="Z32" s="72"/>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A33" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="B33" s="68" t="s">
+      <c r="B33" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="C33" s="69" t="s">
+      <c r="C33" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="D33" s="74"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="74"/>
-      <c r="H33" s="74"/>
-      <c r="I33" s="74"/>
-      <c r="J33" s="74"/>
-      <c r="K33" s="74"/>
-      <c r="L33" s="74"/>
-      <c r="M33" s="74"/>
-      <c r="N33" s="74"/>
-      <c r="O33" s="74"/>
-      <c r="P33" s="74"/>
-      <c r="Q33" s="74"/>
-      <c r="R33" s="74"/>
-      <c r="S33" s="74"/>
-      <c r="T33" s="74"/>
-      <c r="U33" s="74"/>
-      <c r="V33" s="74"/>
-      <c r="W33" s="74"/>
-      <c r="X33" s="74"/>
-      <c r="Y33" s="74"/>
-      <c r="Z33" s="74"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="67" t="s">
+      <c r="D33" s="72"/>
+      <c r="E33" s="72"/>
+      <c r="F33" s="72"/>
+      <c r="G33" s="72"/>
+      <c r="H33" s="72"/>
+      <c r="I33" s="72"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="72"/>
+      <c r="M33" s="72"/>
+      <c r="N33" s="72"/>
+      <c r="O33" s="72"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="72"/>
+      <c r="T33" s="72"/>
+      <c r="U33" s="72"/>
+      <c r="V33" s="72"/>
+      <c r="W33" s="72"/>
+      <c r="X33" s="72"/>
+      <c r="Y33" s="72"/>
+      <c r="Z33" s="72"/>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A34" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="B34" s="68" t="s">
+      <c r="B34" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="69" t="s">
+      <c r="C34" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="D34" s="74"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="74"/>
-      <c r="I34" s="74"/>
-      <c r="J34" s="74"/>
-      <c r="K34" s="74"/>
-      <c r="L34" s="74"/>
-      <c r="M34" s="74"/>
-      <c r="N34" s="74"/>
-      <c r="O34" s="74"/>
-      <c r="P34" s="74"/>
-      <c r="Q34" s="74"/>
-      <c r="R34" s="74"/>
-      <c r="S34" s="74"/>
-      <c r="T34" s="74"/>
-      <c r="U34" s="74"/>
-      <c r="V34" s="74"/>
-      <c r="W34" s="74"/>
-      <c r="X34" s="74"/>
-      <c r="Y34" s="74"/>
-      <c r="Z34" s="74"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="73" t="s">
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="72"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="72"/>
+      <c r="M34" s="72"/>
+      <c r="N34" s="72"/>
+      <c r="O34" s="72"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="72"/>
+      <c r="T34" s="72"/>
+      <c r="U34" s="72"/>
+      <c r="V34" s="72"/>
+      <c r="W34" s="72"/>
+      <c r="X34" s="72"/>
+      <c r="Y34" s="72"/>
+      <c r="Z34" s="72"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="71" t="s">
         <v>85</v>
       </c>
-      <c r="B35" s="71" t="s">
+      <c r="B35" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="C35" s="72" t="s">
+      <c r="C35" s="70" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="67" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="B36" s="68" t="s">
+      <c r="B36" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="C36" s="69" t="s">
+      <c r="C36" s="67" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="67" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="B37" s="68" t="s">
+      <c r="B37" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="C37" s="69" t="s">
+      <c r="C37" s="67" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="73" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="71" t="s">
         <v>89</v>
       </c>
-      <c r="B38" s="71" t="s">
+      <c r="B38" s="69" t="s">
         <v>90</v>
       </c>
-      <c r="C38" s="72" t="s">
+      <c r="C38" s="70" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="68" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="B39" s="68" t="s">
+      <c r="B39" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="C39" s="69" t="s">
+      <c r="C39" s="67" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="67" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="65" t="s">
         <v>92</v>
       </c>
-      <c r="B40" s="68" t="s">
+      <c r="B40" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="C40" s="69" t="s">
+      <c r="C40" s="67" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="67" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="B41" s="68" t="s">
+      <c r="B41" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="C41" s="69" t="s">
+      <c r="C41" s="67" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="73" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="71" t="s">
         <v>94</v>
       </c>
-      <c r="B42" s="71" t="s">
+      <c r="B42" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="C42" s="72" t="s">
+      <c r="C42" s="70" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="68" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="B43" s="68" t="s">
+      <c r="B43" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="C43" s="69" t="s">
+      <c r="C43" s="67" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="67" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="B44" s="68" t="s">
+      <c r="B44" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="C44" s="69" t="s">
+      <c r="C44" s="67" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="67" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="65" t="s">
         <v>98</v>
       </c>
-      <c r="B45" s="68" t="s">
+      <c r="B45" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="C45" s="69" t="s">
+      <c r="C45" s="67" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="73" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="B46" s="71" t="s">
+      <c r="B46" s="69" t="s">
         <v>100</v>
       </c>
-      <c r="C46" s="72" t="s">
+      <c r="C46" s="70" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="68" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="B47" s="68" t="s">
+      <c r="B47" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="69" t="s">
+      <c r="C47" s="67" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="67" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="65" t="s">
         <v>102</v>
       </c>
-      <c r="B48" s="68" t="s">
+      <c r="B48" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="C48" s="69" t="s">
+      <c r="C48" s="67" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="67" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="65" t="s">
         <v>103</v>
       </c>
-      <c r="B49" s="68" t="s">
+      <c r="B49" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="C49" s="69" t="s">
+      <c r="C49" s="67" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="73" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="B50" s="71" t="s">
+      <c r="B50" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="C50" s="72" t="s">
+      <c r="C50" s="70" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="68" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="B51" s="68" t="s">
+      <c r="B51" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="C51" s="69" t="s">
+      <c r="C51" s="67" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="67" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="65" t="s">
         <v>107</v>
       </c>
-      <c r="B52" s="68" t="s">
+      <c r="B52" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="C52" s="69" t="s">
+      <c r="C52" s="67" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="73" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="71" t="s">
         <v>108</v>
       </c>
-      <c r="B53" s="71" t="s">
+      <c r="B53" s="69" t="s">
         <v>109</v>
       </c>
-      <c r="C53" s="72" t="s">
+      <c r="C53" s="70" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="68" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="66" t="s">
         <v>109</v>
       </c>
-      <c r="B54" s="68" t="s">
+      <c r="B54" s="66" t="s">
         <v>109</v>
       </c>
-      <c r="C54" s="69" t="s">
+      <c r="C54" s="67" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="67" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="65" t="s">
         <v>111</v>
       </c>
-      <c r="B55" s="68" t="s">
+      <c r="B55" s="66" t="s">
         <v>109</v>
       </c>
-      <c r="C55" s="69" t="s">
+      <c r="C55" s="67" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="73" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="71" t="s">
         <v>112</v>
       </c>
-      <c r="B56" s="71" t="s">
+      <c r="B56" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="C56" s="72" t="s">
+      <c r="C56" s="70" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="68" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="B57" s="68" t="s">
+      <c r="B57" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="C57" s="69" t="s">
+      <c r="C57" s="67" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="67" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="65" t="s">
         <v>115</v>
       </c>
-      <c r="B58" s="68" t="s">
+      <c r="B58" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="C58" s="69" t="s">
+      <c r="C58" s="67" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="73" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="71" t="s">
         <v>116</v>
       </c>
-      <c r="B59" s="71" t="s">
+      <c r="B59" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="C59" s="72" t="s">
+      <c r="C59" s="70" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="68" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="B60" s="68" t="s">
+      <c r="B60" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="C60" s="69" t="s">
+      <c r="C60" s="67" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="67" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="65" t="s">
         <v>119</v>
       </c>
-      <c r="B61" s="68" t="s">
+      <c r="B61" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="C61" s="69" t="s">
+      <c r="C61" s="67" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="73" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="71" t="s">
         <v>120</v>
       </c>
-      <c r="B62" s="71" t="s">
+      <c r="B62" s="69" t="s">
         <v>121</v>
       </c>
-      <c r="C62" s="72" t="s">
+      <c r="C62" s="70" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="68" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="B63" s="68" t="s">
+      <c r="B63" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="C63" s="69" t="s">
+      <c r="C63" s="67" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="67" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="65" t="s">
         <v>123</v>
       </c>
-      <c r="B64" s="68" t="s">
+      <c r="B64" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="C64" s="69" t="s">
+      <c r="C64" s="67" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="73" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="71" t="s">
         <v>124</v>
       </c>
-      <c r="B65" s="71" t="s">
+      <c r="B65" s="69" t="s">
         <v>125</v>
       </c>
-      <c r="C65" s="72" t="s">
+      <c r="C65" s="70" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="75" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="73" t="s">
         <v>125</v>
       </c>
-      <c r="B66" s="75" t="s">
+      <c r="B66" s="73" t="s">
         <v>125</v>
       </c>
-      <c r="C66" s="76" t="s">
+      <c r="C66" s="74" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="77" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="75" t="s">
         <v>127</v>
       </c>
-      <c r="B67" s="75" t="s">
+      <c r="B67" s="73" t="s">
         <v>125</v>
       </c>
-      <c r="C67" s="76" t="s">
+      <c r="C67" s="74" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="73" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="B68" s="71" t="s">
+      <c r="B68" s="69" t="s">
         <v>129</v>
       </c>
-      <c r="C68" s="72" t="s">
+      <c r="C68" s="70" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="68" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="66" t="s">
         <v>129</v>
       </c>
-      <c r="B69" s="68" t="s">
+      <c r="B69" s="66" t="s">
         <v>129</v>
       </c>
-      <c r="C69" s="69" t="s">
+      <c r="C69" s="67" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="67" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="65" t="s">
         <v>131</v>
       </c>
-      <c r="B70" s="68" t="s">
+      <c r="B70" s="66" t="s">
         <v>129</v>
       </c>
-      <c r="C70" s="69" t="s">
+      <c r="C70" s="67" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="73" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="B71" s="71" t="s">
+      <c r="B71" s="69" t="s">
         <v>133</v>
       </c>
-      <c r="C71" s="72" t="s">
+      <c r="C71" s="70" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="68" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="66" t="s">
         <v>133</v>
       </c>
-      <c r="B72" s="68" t="s">
+      <c r="B72" s="66" t="s">
         <v>133</v>
       </c>
-      <c r="C72" s="69" t="s">
+      <c r="C72" s="67" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="67" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="B73" s="68" t="s">
+      <c r="B73" s="66" t="s">
         <v>133</v>
       </c>
-      <c r="C73" s="69" t="s">
+      <c r="C73" s="67" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="67" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="65" t="s">
         <v>136</v>
       </c>
-      <c r="B74" s="68" t="s">
+      <c r="B74" s="66" t="s">
         <v>133</v>
       </c>
-      <c r="C74" s="69" t="s">
+      <c r="C74" s="67" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="73" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="71" t="s">
         <v>137</v>
       </c>
-      <c r="B75" s="71" t="s">
+      <c r="B75" s="69" t="s">
         <v>138</v>
       </c>
-      <c r="C75" s="72" t="s">
+      <c r="C75" s="70" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="68" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="66" t="s">
         <v>138</v>
       </c>
-      <c r="B76" s="68" t="s">
+      <c r="B76" s="66" t="s">
         <v>138</v>
       </c>
-      <c r="C76" s="69" t="s">
+      <c r="C76" s="67" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="67" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="65" t="s">
         <v>140</v>
       </c>
-      <c r="B77" s="68" t="s">
+      <c r="B77" s="66" t="s">
         <v>138</v>
       </c>
-      <c r="C77" s="69" t="s">
+      <c r="C77" s="67" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="73" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="71" t="s">
         <v>141</v>
       </c>
-      <c r="B78" s="71" t="s">
+      <c r="B78" s="69" t="s">
         <v>142</v>
       </c>
-      <c r="C78" s="72" t="s">
+      <c r="C78" s="70" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="68" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="66" t="s">
         <v>142</v>
       </c>
-      <c r="B79" s="68" t="s">
+      <c r="B79" s="66" t="s">
         <v>142</v>
       </c>
-      <c r="C79" s="69" t="s">
+      <c r="C79" s="67" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="67" t="s">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="65" t="s">
         <v>144</v>
       </c>
-      <c r="B80" s="68" t="s">
+      <c r="B80" s="66" t="s">
         <v>142</v>
       </c>
-      <c r="C80" s="69" t="s">
+      <c r="C80" s="67" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="67" t="s">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="B81" s="68" t="s">
+      <c r="B81" s="66" t="s">
         <v>142</v>
       </c>
-      <c r="C81" s="69" t="s">
+      <c r="C81" s="67" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="67" t="s">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="65" t="s">
         <v>146</v>
       </c>
-      <c r="B82" s="68" t="s">
+      <c r="B82" s="66" t="s">
         <v>142</v>
       </c>
-      <c r="C82" s="69" t="s">
+      <c r="C82" s="67" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="73" t="s">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="71" t="s">
         <v>147</v>
       </c>
-      <c r="B83" s="71" t="s">
+      <c r="B83" s="69" t="s">
         <v>148</v>
       </c>
-      <c r="C83" s="72" t="s">
+      <c r="C83" s="70" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="68" t="s">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="66" t="s">
         <v>148</v>
       </c>
-      <c r="B84" s="68" t="s">
+      <c r="B84" s="66" t="s">
         <v>148</v>
       </c>
-      <c r="C84" s="69" t="s">
+      <c r="C84" s="67" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="78" t="s">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="76" t="s">
         <v>150</v>
       </c>
-      <c r="B85" s="68" t="s">
+      <c r="B85" s="66" t="s">
         <v>148</v>
       </c>
-      <c r="C85" s="69" t="s">
+      <c r="C85" s="67" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="78" t="s">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="76" t="s">
         <v>151</v>
       </c>
-      <c r="B86" s="68" t="s">
+      <c r="B86" s="66" t="s">
         <v>148</v>
       </c>
-      <c r="C86" s="69" t="s">
+      <c r="C86" s="67" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="73" t="s">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="71" t="s">
         <v>152</v>
       </c>
-      <c r="B87" s="71" t="s">
+      <c r="B87" s="69" t="s">
         <v>153</v>
       </c>
-      <c r="C87" s="72" t="s">
+      <c r="C87" s="70" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="68" t="s">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="66" t="s">
         <v>153</v>
       </c>
-      <c r="B88" s="68" t="s">
+      <c r="B88" s="66" t="s">
         <v>153</v>
       </c>
-      <c r="C88" s="69" t="s">
+      <c r="C88" s="67" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="67" t="s">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="65" t="s">
         <v>155</v>
       </c>
-      <c r="B89" s="68" t="s">
+      <c r="B89" s="66" t="s">
         <v>153</v>
       </c>
-      <c r="C89" s="69" t="s">
+      <c r="C89" s="67" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="73" t="s">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="71" t="s">
         <v>156</v>
       </c>
-      <c r="B90" s="71" t="s">
+      <c r="B90" s="69" t="s">
         <v>157</v>
       </c>
-      <c r="C90" s="72" t="s">
+      <c r="C90" s="70" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="68" t="s">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="66" t="s">
         <v>157</v>
       </c>
-      <c r="B91" s="68" t="s">
+      <c r="B91" s="66" t="s">
         <v>157</v>
       </c>
-      <c r="C91" s="69" t="s">
+      <c r="C91" s="67" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="67" t="s">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="65" t="s">
         <v>159</v>
       </c>
-      <c r="B92" s="68" t="s">
+      <c r="B92" s="66" t="s">
         <v>157</v>
       </c>
-      <c r="C92" s="69" t="s">
+      <c r="C92" s="67" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="67" t="s">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="65" t="s">
         <v>160</v>
       </c>
-      <c r="B93" s="68" t="s">
+      <c r="B93" s="66" t="s">
         <v>157</v>
       </c>
-      <c r="C93" s="69" t="s">
+      <c r="C93" s="67" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="73" t="s">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="71" t="s">
         <v>161</v>
       </c>
-      <c r="B94" s="71" t="s">
+      <c r="B94" s="69" t="s">
         <v>162</v>
       </c>
-      <c r="C94" s="72" t="s">
+      <c r="C94" s="70" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="68" t="s">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="66" t="s">
         <v>162</v>
       </c>
-      <c r="B95" s="68" t="s">
+      <c r="B95" s="66" t="s">
         <v>162</v>
       </c>
-      <c r="C95" s="69" t="s">
+      <c r="C95" s="67" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="67" t="s">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="65" t="s">
         <v>164</v>
       </c>
-      <c r="B96" s="68" t="s">
+      <c r="B96" s="66" t="s">
         <v>162</v>
       </c>
-      <c r="C96" s="69" t="s">
+      <c r="C96" s="67" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="67" t="s">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="65" t="s">
         <v>165</v>
       </c>
-      <c r="B97" s="68" t="s">
+      <c r="B97" s="66" t="s">
         <v>162</v>
       </c>
-      <c r="C97" s="69" t="s">
+      <c r="C97" s="67" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="73" t="s">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="71" t="s">
         <v>166</v>
       </c>
-      <c r="B98" s="71" t="s">
+      <c r="B98" s="69" t="s">
         <v>167</v>
       </c>
-      <c r="C98" s="72" t="s">
+      <c r="C98" s="70" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="68" t="s">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="66" t="s">
         <v>167</v>
       </c>
-      <c r="B99" s="68" t="s">
+      <c r="B99" s="66" t="s">
         <v>167</v>
       </c>
-      <c r="C99" s="69" t="s">
+      <c r="C99" s="67" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="67" t="s">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="65" t="s">
         <v>169</v>
       </c>
-      <c r="B100" s="68" t="s">
+      <c r="B100" s="66" t="s">
         <v>167</v>
       </c>
-      <c r="C100" s="69" t="s">
+      <c r="C100" s="67" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="67" t="s">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="65" t="s">
         <v>170</v>
       </c>
-      <c r="B101" s="68" t="s">
+      <c r="B101" s="66" t="s">
         <v>167</v>
       </c>
-      <c r="C101" s="69" t="s">
+      <c r="C101" s="67" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="73" t="s">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="71" t="s">
         <v>171</v>
       </c>
-      <c r="B102" s="71" t="s">
+      <c r="B102" s="69" t="s">
         <v>172</v>
       </c>
-      <c r="C102" s="72" t="s">
+      <c r="C102" s="70" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="68" t="s">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="66" t="s">
         <v>172</v>
       </c>
-      <c r="B103" s="68" t="s">
+      <c r="B103" s="66" t="s">
         <v>172</v>
       </c>
-      <c r="C103" s="69" t="s">
+      <c r="C103" s="67" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="67" t="s">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="65" t="s">
         <v>174</v>
       </c>
-      <c r="B104" s="68" t="s">
+      <c r="B104" s="66" t="s">
         <v>172</v>
       </c>
-      <c r="C104" s="69" t="s">
+      <c r="C104" s="67" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="67" t="s">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="65" t="s">
         <v>175</v>
       </c>
-      <c r="B105" s="68" t="s">
+      <c r="B105" s="66" t="s">
         <v>172</v>
       </c>
-      <c r="C105" s="69" t="s">
+      <c r="C105" s="67" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="73" t="s">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="B106" s="71" t="s">
+      <c r="B106" s="69" t="s">
         <v>177</v>
       </c>
-      <c r="C106" s="72" t="s">
+      <c r="C106" s="70" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="68" t="s">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="66" t="s">
         <v>177</v>
       </c>
-      <c r="B107" s="68" t="s">
+      <c r="B107" s="66" t="s">
         <v>177</v>
       </c>
-      <c r="C107" s="69" t="s">
+      <c r="C107" s="67" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="67" t="s">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="65" t="s">
         <v>179</v>
       </c>
-      <c r="B108" s="68" t="s">
+      <c r="B108" s="66" t="s">
         <v>177</v>
       </c>
-      <c r="C108" s="69" t="s">
+      <c r="C108" s="67" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="67" t="s">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="65" t="s">
         <v>180</v>
       </c>
-      <c r="B109" s="68" t="s">
+      <c r="B109" s="66" t="s">
         <v>177</v>
       </c>
-      <c r="C109" s="69" t="s">
+      <c r="C109" s="67" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="73" t="s">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="71" t="s">
         <v>181</v>
       </c>
-      <c r="B110" s="71" t="s">
+      <c r="B110" s="69" t="s">
         <v>182</v>
       </c>
-      <c r="C110" s="72" t="s">
+      <c r="C110" s="70" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="68" t="s">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="66" t="s">
         <v>182</v>
       </c>
-      <c r="B111" s="68" t="s">
+      <c r="B111" s="66" t="s">
         <v>182</v>
       </c>
-      <c r="C111" s="69" t="s">
+      <c r="C111" s="67" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="67" t="s">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="65" t="s">
         <v>184</v>
       </c>
-      <c r="B112" s="68" t="s">
+      <c r="B112" s="66" t="s">
         <v>182</v>
       </c>
-      <c r="C112" s="69" t="s">
+      <c r="C112" s="67" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="73" t="s">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="71" t="s">
         <v>185</v>
       </c>
-      <c r="B113" s="71" t="s">
+      <c r="B113" s="69" t="s">
         <v>186</v>
       </c>
-      <c r="C113" s="72" t="s">
+      <c r="C113" s="70" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="68" t="s">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="66" t="s">
         <v>186</v>
       </c>
-      <c r="B114" s="68" t="s">
+      <c r="B114" s="66" t="s">
         <v>186</v>
       </c>
-      <c r="C114" s="69" t="s">
+      <c r="C114" s="67" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="67" t="s">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="65" t="s">
         <v>188</v>
       </c>
-      <c r="B115" s="68" t="s">
+      <c r="B115" s="66" t="s">
         <v>186</v>
       </c>
-      <c r="C115" s="69" t="s">
+      <c r="C115" s="67" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="73" t="s">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="71" t="s">
         <v>189</v>
       </c>
-      <c r="B116" s="71" t="s">
+      <c r="B116" s="69" t="s">
         <v>190</v>
       </c>
-      <c r="C116" s="72" t="s">
+      <c r="C116" s="70" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="68" t="s">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="B117" s="68" t="s">
+      <c r="B117" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="C117" s="69" t="s">
+      <c r="C117" s="67" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="67" t="s">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="65" t="s">
         <v>192</v>
       </c>
-      <c r="B118" s="68" t="s">
+      <c r="B118" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="C118" s="69" t="s">
+      <c r="C118" s="67" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="73" t="s">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="71" t="s">
         <v>193</v>
       </c>
-      <c r="B119" s="71" t="s">
+      <c r="B119" s="69" t="s">
         <v>194</v>
       </c>
-      <c r="C119" s="72" t="s">
+      <c r="C119" s="70" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="68" t="s">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="66" t="s">
         <v>194</v>
       </c>
-      <c r="B120" s="68" t="s">
+      <c r="B120" s="66" t="s">
         <v>194</v>
       </c>
-      <c r="C120" s="69" t="s">
+      <c r="C120" s="67" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="67" t="s">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="65" t="s">
         <v>196</v>
       </c>
-      <c r="B121" s="68" t="s">
+      <c r="B121" s="66" t="s">
         <v>194</v>
       </c>
-      <c r="C121" s="69" t="s">
+      <c r="C121" s="67" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="73" t="s">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="71" t="s">
         <v>197</v>
       </c>
-      <c r="B122" s="71" t="s">
+      <c r="B122" s="69" t="s">
         <v>198</v>
       </c>
-      <c r="C122" s="72" t="s">
+      <c r="C122" s="70" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="68" t="s">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="66" t="s">
         <v>198</v>
       </c>
-      <c r="B123" s="68" t="s">
+      <c r="B123" s="66" t="s">
         <v>198</v>
       </c>
-      <c r="C123" s="69" t="s">
+      <c r="C123" s="67" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="67" t="s">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="65" t="s">
         <v>200</v>
       </c>
-      <c r="B124" s="68" t="s">
+      <c r="B124" s="66" t="s">
         <v>198</v>
       </c>
-      <c r="C124" s="69" t="s">
+      <c r="C124" s="67" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="73" t="s">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="71" t="s">
         <v>201</v>
       </c>
-      <c r="B125" s="71" t="s">
+      <c r="B125" s="69" t="s">
         <v>202</v>
       </c>
-      <c r="C125" s="72" t="s">
+      <c r="C125" s="70" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="68" t="s">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="66" t="s">
         <v>202</v>
       </c>
-      <c r="B126" s="68" t="s">
+      <c r="B126" s="66" t="s">
         <v>202</v>
       </c>
-      <c r="C126" s="69" t="s">
+      <c r="C126" s="67" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="67" t="s">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="65" t="s">
         <v>204</v>
       </c>
-      <c r="B127" s="68" t="s">
+      <c r="B127" s="66" t="s">
         <v>202</v>
       </c>
-      <c r="C127" s="69" t="s">
+      <c r="C127" s="67" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="73" t="s">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="71" t="s">
         <v>205</v>
       </c>
-      <c r="B128" s="71" t="s">
+      <c r="B128" s="69" t="s">
         <v>206</v>
       </c>
-      <c r="C128" s="72" t="s">
+      <c r="C128" s="70" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="67" t="s">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="65" t="s">
         <v>206</v>
       </c>
-      <c r="B129" s="68" t="s">
+      <c r="B129" s="66" t="s">
         <v>206</v>
       </c>
-      <c r="C129" s="69" t="s">
+      <c r="C129" s="67" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="67" t="s">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="65" t="s">
         <v>208</v>
       </c>
-      <c r="B130" s="68" t="s">
+      <c r="B130" s="66" t="s">
         <v>206</v>
       </c>
-      <c r="C130" s="69" t="s">
+      <c r="C130" s="67" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="73" t="s">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="71" t="s">
         <v>209</v>
       </c>
-      <c r="B131" s="71" t="s">
+      <c r="B131" s="69" t="s">
         <v>210</v>
       </c>
-      <c r="C131" s="72" t="s">
+      <c r="C131" s="70" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="67" t="s">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="65" t="s">
         <v>210</v>
       </c>
-      <c r="B132" s="68" t="s">
+      <c r="B132" s="66" t="s">
         <v>210</v>
       </c>
-      <c r="C132" s="69" t="s">
+      <c r="C132" s="67" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="67" t="s">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="65" t="s">
         <v>212</v>
       </c>
-      <c r="B133" s="68" t="s">
+      <c r="B133" s="66" t="s">
         <v>210</v>
       </c>
-      <c r="C133" s="69" t="s">
+      <c r="C133" s="67" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="73" t="s">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="71" t="s">
         <v>213</v>
       </c>
-      <c r="B134" s="71" t="s">
+      <c r="B134" s="69" t="s">
         <v>214</v>
       </c>
-      <c r="C134" s="72" t="s">
+      <c r="C134" s="70" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="67" t="s">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="65" t="s">
         <v>214</v>
       </c>
-      <c r="B135" s="68" t="s">
+      <c r="B135" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="C135" s="69" t="s">
+      <c r="C135" s="67" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="67" t="s">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="65" t="s">
         <v>216</v>
       </c>
-      <c r="B136" s="68" t="s">
+      <c r="B136" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="C136" s="69" t="s">
+      <c r="C136" s="67" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="73" t="s">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="71" t="s">
         <v>217</v>
       </c>
-      <c r="B137" s="71" t="s">
+      <c r="B137" s="69" t="s">
         <v>218</v>
       </c>
-      <c r="C137" s="72" t="s">
+      <c r="C137" s="70" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="67" t="s">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="65" t="s">
         <v>218</v>
       </c>
-      <c r="B138" s="68" t="s">
+      <c r="B138" s="66" t="s">
         <v>218</v>
       </c>
-      <c r="C138" s="69" t="s">
+      <c r="C138" s="67" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="67" t="s">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="65" t="s">
         <v>220</v>
       </c>
-      <c r="B139" s="68" t="s">
+      <c r="B139" s="66" t="s">
         <v>218</v>
       </c>
-      <c r="C139" s="69" t="s">
+      <c r="C139" s="67" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="73" t="s">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="71" t="s">
         <v>221</v>
       </c>
-      <c r="B140" s="71" t="s">
+      <c r="B140" s="69" t="s">
         <v>222</v>
       </c>
-      <c r="C140" s="72" t="s">
+      <c r="C140" s="70" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="67" t="s">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="65" t="s">
         <v>222</v>
       </c>
-      <c r="B141" s="68" t="s">
+      <c r="B141" s="66" t="s">
         <v>222</v>
       </c>
-      <c r="C141" s="69" t="s">
+      <c r="C141" s="67" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="67" t="s">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="65" t="s">
         <v>224</v>
       </c>
-      <c r="B142" s="68" t="s">
+      <c r="B142" s="66" t="s">
         <v>222</v>
       </c>
-      <c r="C142" s="69" t="s">
+      <c r="C142" s="67" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="73" t="s">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="71" t="s">
         <v>225</v>
       </c>
-      <c r="B143" s="71" t="s">
+      <c r="B143" s="69" t="s">
         <v>226</v>
       </c>
-      <c r="C143" s="72" t="s">
+      <c r="C143" s="70" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="67" t="s">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="65" t="s">
         <v>226</v>
       </c>
-      <c r="B144" s="68" t="s">
+      <c r="B144" s="66" t="s">
         <v>226</v>
       </c>
-      <c r="C144" s="69" t="s">
+      <c r="C144" s="67" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="67" t="s">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="65" t="s">
         <v>228</v>
       </c>
-      <c r="B145" s="68" t="s">
+      <c r="B145" s="66" t="s">
         <v>226</v>
       </c>
-      <c r="C145" s="69" t="s">
+      <c r="C145" s="67" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="73" t="s">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="71" t="s">
         <v>229</v>
       </c>
-      <c r="B146" s="71" t="s">
+      <c r="B146" s="69" t="s">
         <v>230</v>
       </c>
-      <c r="C146" s="72" t="s">
+      <c r="C146" s="70" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="67" t="s">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="65" t="s">
         <v>230</v>
       </c>
-      <c r="B147" s="68" t="s">
+      <c r="B147" s="66" t="s">
         <v>230</v>
       </c>
-      <c r="C147" s="69" t="s">
+      <c r="C147" s="67" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="67" t="s">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="65" t="s">
         <v>232</v>
       </c>
-      <c r="B148" s="68" t="s">
+      <c r="B148" s="66" t="s">
         <v>230</v>
       </c>
-      <c r="C148" s="69" t="s">
+      <c r="C148" s="67" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="67" t="s">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="65" t="s">
         <v>229</v>
       </c>
-      <c r="B149" s="68" t="s">
+      <c r="B149" s="66" t="s">
         <v>230</v>
       </c>
-      <c r="C149" s="69" t="s">
+      <c r="C149" s="67" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="73" t="s">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="71" t="s">
         <v>233</v>
       </c>
-      <c r="B150" s="71" t="s">
+      <c r="B150" s="69" t="s">
         <v>234</v>
       </c>
-      <c r="C150" s="72" t="s">
+      <c r="C150" s="70" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="67" t="s">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="65" t="s">
         <v>234</v>
       </c>
-      <c r="B151" s="68" t="s">
+      <c r="B151" s="66" t="s">
         <v>234</v>
       </c>
-      <c r="C151" s="69" t="s">
+      <c r="C151" s="67" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="67" t="s">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="65" t="s">
         <v>236</v>
       </c>
-      <c r="B152" s="68" t="s">
+      <c r="B152" s="66" t="s">
         <v>234</v>
       </c>
-      <c r="C152" s="69" t="s">
+      <c r="C152" s="67" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="67" t="s">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="65" t="s">
         <v>237</v>
       </c>
-      <c r="B153" s="68" t="s">
+      <c r="B153" s="66" t="s">
         <v>234</v>
       </c>
-      <c r="C153" s="69" t="s">
+      <c r="C153" s="67" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="73" t="s">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="71" t="s">
         <v>238</v>
       </c>
-      <c r="B154" s="71" t="s">
+      <c r="B154" s="69" t="s">
         <v>239</v>
       </c>
-      <c r="C154" s="72" t="s">
+      <c r="C154" s="70" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="67" t="s">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="65" t="s">
         <v>239</v>
       </c>
-      <c r="B155" s="68" t="s">
+      <c r="B155" s="66" t="s">
         <v>239</v>
       </c>
-      <c r="C155" s="69" t="s">
+      <c r="C155" s="67" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="67" t="s">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="65" t="s">
         <v>241</v>
       </c>
-      <c r="B156" s="68" t="s">
+      <c r="B156" s="66" t="s">
         <v>239</v>
       </c>
-      <c r="C156" s="69" t="s">
+      <c r="C156" s="67" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="73" t="s">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="71" t="s">
         <v>242</v>
       </c>
-      <c r="B157" s="71" t="s">
+      <c r="B157" s="69" t="s">
         <v>243</v>
       </c>
-      <c r="C157" s="72" t="s">
+      <c r="C157" s="70" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="67" t="s">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="65" t="s">
         <v>243</v>
       </c>
-      <c r="B158" s="68" t="s">
+      <c r="B158" s="66" t="s">
         <v>243</v>
       </c>
-      <c r="C158" s="69" t="s">
+      <c r="C158" s="67" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="67" t="s">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="65" t="s">
         <v>245</v>
       </c>
-      <c r="B159" s="68" t="s">
+      <c r="B159" s="66" t="s">
         <v>243</v>
       </c>
-      <c r="C159" s="69" t="s">
+      <c r="C159" s="67" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="73" t="s">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="71" t="s">
         <v>246</v>
       </c>
-      <c r="B160" s="71" t="s">
+      <c r="B160" s="69" t="s">
         <v>247</v>
       </c>
-      <c r="C160" s="72" t="s">
+      <c r="C160" s="70" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="67" t="s">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="65" t="s">
         <v>247</v>
       </c>
-      <c r="B161" s="68" t="s">
+      <c r="B161" s="66" t="s">
         <v>247</v>
       </c>
-      <c r="C161" s="69" t="s">
+      <c r="C161" s="67" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="67" t="s">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="65" t="s">
         <v>136</v>
       </c>
-      <c r="B162" s="68" t="s">
+      <c r="B162" s="66" t="s">
         <v>247</v>
       </c>
-      <c r="C162" s="69" t="s">
+      <c r="C162" s="67" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="73" t="s">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="71" t="s">
         <v>249</v>
       </c>
-      <c r="B163" s="71" t="s">
+      <c r="B163" s="69" t="s">
         <v>250</v>
       </c>
-      <c r="C163" s="72" t="s">
+      <c r="C163" s="70" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="67" t="s">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="65" t="s">
         <v>250</v>
       </c>
-      <c r="B164" s="68" t="s">
+      <c r="B164" s="66" t="s">
         <v>250</v>
       </c>
-      <c r="C164" s="69" t="s">
+      <c r="C164" s="67" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="67" t="s">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="65" t="s">
         <v>252</v>
       </c>
-      <c r="B165" s="68" t="s">
+      <c r="B165" s="66" t="s">
         <v>250</v>
       </c>
-      <c r="C165" s="69" t="s">
+      <c r="C165" s="67" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="73" t="s">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="71" t="s">
         <v>253</v>
       </c>
-      <c r="B166" s="71" t="s">
+      <c r="B166" s="69" t="s">
         <v>254</v>
       </c>
-      <c r="C166" s="72" t="s">
+      <c r="C166" s="70" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="67" t="s">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="65" t="s">
         <v>254</v>
       </c>
-      <c r="B167" s="68" t="s">
+      <c r="B167" s="66" t="s">
         <v>254</v>
       </c>
-      <c r="C167" s="69" t="s">
+      <c r="C167" s="67" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="67" t="s">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="65" t="s">
         <v>256</v>
       </c>
-      <c r="B168" s="68" t="s">
+      <c r="B168" s="66" t="s">
         <v>254</v>
       </c>
-      <c r="C168" s="69" t="s">
+      <c r="C168" s="67" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="73" t="s">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="71" t="s">
         <v>257</v>
       </c>
-      <c r="B169" s="71" t="s">
+      <c r="B169" s="69" t="s">
         <v>258</v>
       </c>
-      <c r="C169" s="72" t="s">
+      <c r="C169" s="70" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="68" t="s">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="66" t="s">
         <v>258</v>
       </c>
-      <c r="B170" s="68" t="s">
+      <c r="B170" s="66" t="s">
         <v>258</v>
       </c>
-      <c r="C170" s="69" t="s">
+      <c r="C170" s="67" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="67" t="s">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="65" t="s">
         <v>260</v>
       </c>
-      <c r="B171" s="68" t="s">
+      <c r="B171" s="66" t="s">
         <v>258</v>
       </c>
-      <c r="C171" s="69" t="s">
+      <c r="C171" s="67" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="73" t="s">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="71" t="s">
         <v>261</v>
       </c>
-      <c r="B172" s="71" t="s">
+      <c r="B172" s="69" t="s">
         <v>262</v>
       </c>
-      <c r="C172" s="72" t="s">
+      <c r="C172" s="70" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="68" t="s">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="66" t="s">
         <v>262</v>
       </c>
-      <c r="B173" s="68" t="s">
+      <c r="B173" s="66" t="s">
         <v>262</v>
       </c>
-      <c r="C173" s="69" t="s">
+      <c r="C173" s="67" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="67" t="s">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="65" t="s">
         <v>264</v>
       </c>
-      <c r="B174" s="68" t="s">
+      <c r="B174" s="66" t="s">
         <v>262</v>
       </c>
-      <c r="C174" s="69" t="s">
+      <c r="C174" s="67" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="67" t="s">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="65" t="s">
         <v>265</v>
       </c>
-      <c r="B175" s="68" t="s">
+      <c r="B175" s="66" t="s">
         <v>262</v>
       </c>
-      <c r="C175" s="69" t="s">
+      <c r="C175" s="67" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="73" t="s">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="71" t="s">
         <v>266</v>
       </c>
-      <c r="B176" s="71" t="s">
+      <c r="B176" s="69" t="s">
         <v>267</v>
       </c>
-      <c r="C176" s="72" t="s">
+      <c r="C176" s="70" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="68" t="s">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="66" t="s">
         <v>267</v>
       </c>
-      <c r="B177" s="68" t="s">
+      <c r="B177" s="66" t="s">
         <v>267</v>
       </c>
-      <c r="C177" s="69" t="s">
+      <c r="C177" s="67" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="67" t="s">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="65" t="s">
         <v>269</v>
       </c>
-      <c r="B178" s="68" t="s">
+      <c r="B178" s="66" t="s">
         <v>267</v>
       </c>
-      <c r="C178" s="69" t="s">
+      <c r="C178" s="67" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="73" t="s">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="71" t="s">
         <v>270</v>
       </c>
-      <c r="B179" s="71" t="s">
+      <c r="B179" s="69" t="s">
         <v>271</v>
       </c>
-      <c r="C179" s="72" t="s">
+      <c r="C179" s="70" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="68" t="s">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="66" t="s">
         <v>271</v>
       </c>
-      <c r="B180" s="68" t="s">
+      <c r="B180" s="66" t="s">
         <v>271</v>
       </c>
-      <c r="C180" s="69" t="s">
+      <c r="C180" s="67" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="79" t="s">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="77" t="s">
         <v>273</v>
       </c>
-      <c r="B181" s="68" t="s">
+      <c r="B181" s="66" t="s">
         <v>271</v>
       </c>
-      <c r="C181" s="69" t="s">
+      <c r="C181" s="67" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="73" t="s">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="71" t="s">
         <v>274</v>
       </c>
-      <c r="B182" s="71" t="s">
+      <c r="B182" s="69" t="s">
         <v>275</v>
       </c>
-      <c r="C182" s="72" t="s">
+      <c r="C182" s="70" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="67" t="s">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="65" t="s">
         <v>275</v>
       </c>
-      <c r="B183" s="68" t="s">
+      <c r="B183" s="66" t="s">
         <v>275</v>
       </c>
-      <c r="C183" s="69" t="s">
+      <c r="C183" s="67" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="67" t="s">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="65" t="s">
         <v>277</v>
       </c>
-      <c r="B184" s="68" t="s">
+      <c r="B184" s="66" t="s">
         <v>275</v>
       </c>
-      <c r="C184" s="69" t="s">
+      <c r="C184" s="67" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="67" t="s">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="65" t="s">
         <v>278</v>
       </c>
-      <c r="B185" s="68" t="s">
+      <c r="B185" s="66" t="s">
         <v>275</v>
       </c>
-      <c r="C185" s="69" t="s">
+      <c r="C185" s="67" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="80" t="s">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="78" t="s">
         <v>279</v>
       </c>
-      <c r="B186" s="81" t="s">
+      <c r="B186" s="79" t="s">
         <v>275</v>
       </c>
-      <c r="C186" s="82" t="s">
+      <c r="C186" s="80" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="187" ht="58.5" customHeight="1">
-      <c r="A187" s="83" t="s">
+    <row r="187" ht="58.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="81" t="s">
         <v>280</v>
       </c>
-      <c r="B187" s="84"/>
-      <c r="C187" s="85"/>
+      <c r="B187" s="82"/>
+      <c r="C187" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A187:C187"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:D87"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.43"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="57.43"/>
-    <col customWidth="1" min="4" max="4" width="19.71"/>
-    <col customWidth="1" min="5" max="5" width="64.86"/>
+    <col min="1" max="1" width="57.43" customWidth="1"/>
+    <col min="4" max="4" width="19.71" customWidth="1"/>
+    <col min="5" max="5" width="64.86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="54.0" customHeight="1">
-      <c r="A1" s="86" t="s">
+    <row r="1" ht="54" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="84" t="s">
         <v>281</v>
       </c>
-      <c r="B1" s="87" t="s">
+      <c r="B1" s="85" t="s">
         <v>282</v>
       </c>
-      <c r="C1" s="87" t="s">
+      <c r="C1" s="85" t="s">
         <v>283</v>
       </c>
-      <c r="D1" s="88" t="s">
+      <c r="D1" s="86" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D2)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"Pokemon Card Game Scarlet &amp; Violet 151 sv2a Booster Box")</f>
         <v>Pokemon Card Game Scarlet &amp; Violet 151 sv2a Booster Box</v>
       </c>
       <c r="D2" s="5">
-        <v>151.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D3)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D4)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D5)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"Pokemon Card Game Sword &amp; Shield Lost Abyss s11 Booster Box")</f>
         <v>Pokemon Card Game Sword &amp; Shield Lost Abyss s11 Booster Box</v>
@@ -6827,13 +7226,13 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D6)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D7)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"Pokemon Card Game Scarlet &amp; Violet Clay Burst sv2d Booster Box")</f>
         <v>Pokemon Card Game Scarlet &amp; Violet Clay Burst sv2d Booster Box</v>
@@ -6842,7 +7241,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D8)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"Pokemon Card Game Sword &amp; Shield VSTAR Universe s12a")</f>
         <v>Pokemon Card Game Sword &amp; Shield VSTAR Universe s12a</v>
@@ -6851,484 +7250,483 @@
         <v>165</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D9)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"Pokemon Card Game Scarlet &amp; Violet 151 sv2a Booster Box")</f>
         <v>Pokemon Card Game Scarlet &amp; Violet 151 sv2a Booster Box</v>
       </c>
       <c r="D9" s="5">
-        <v>151.0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D10)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D11)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D12)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D13)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D14)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D15)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D16)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D17)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D18)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D19)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D20)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D21)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D22)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D23)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D24)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D25)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D26)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D27)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D28)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D29)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D30)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D31)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D32)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D33)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D34)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D35)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D36)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D37)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D38)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D39)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D40)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D41)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D42)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D43)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D44)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D45)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D46)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D47)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D48)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D49)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D50)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D51)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D52)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D53)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D54)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D55)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D56)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D57)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D58)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D59)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D60)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D61)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D62)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D63)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D64)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D65)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D66)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D67)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D68)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D69)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D70)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D71)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D72)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D73)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D74)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D75)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D76)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D77)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D78)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D79)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D80)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D81)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D82)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D83)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D84)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D85)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D86)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IFERROR(VLOOKUP(TRIM(TO_TEXT(D87)), ITEM_MASTER!A:C, 3, FALSE), ""NOT FOUND"")"),"NOT FOUND")</f>
         <v>NOT FOUND</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>